--- a/إجمالي_مبيعات_المناديب_31-7-2025_إلى_31-7-2026.xlsx
+++ b/إجمالي_مبيعات_المناديب_31-7-2025_إلى_31-7-2026.xlsx
@@ -62,7 +62,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>مبيعات السيارة 6-7 (صافي بعد المرتجع شامل الضريبة)</t>
+          <t>مبيعات السيارة 6-7 (صافي بعد المرتجع)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
         <v/>
       </c>
       <c r="E5" s="4">
-        <f>SUMIFS('مبيعات السيارات 6-7 2026'!J2:J57,'مبيعات السيارات 6-7 2026'!C2:C57,"VHC-1219")</f>
+        <f>SUMIFS('مبيعات السيارات 6-7 2026'!H2:H57,'مبيعات السيارات 6-7 2026'!C2:C57,"VHC-1219")</f>
         <v/>
       </c>
       <c r="F5" s="4">
@@ -620,7 +620,7 @@
         <v/>
       </c>
       <c r="E6" s="4">
-        <f>SUMIFS('مبيعات السيارات 6-7 2026'!J2:J57,'مبيعات السيارات 6-7 2026'!C2:C57,"VHC-3010")</f>
+        <f>SUMIFS('مبيعات السيارات 6-7 2026'!H2:H57,'مبيعات السيارات 6-7 2026'!C2:C57,"VHC-3010")</f>
         <v/>
       </c>
       <c r="F6" s="4">
@@ -698,7 +698,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>ملاحظات المراجعة:</t>
+          <t>ملاحظات المراجعة (كل الأرقام بالقيمة الإجمالية كما هي بالمستندات):</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2) عصمت: عقدان WHT-2756 و WHT-2758 (16,810.00) موجودان في سجل العقود فقط، بدون فاتورة مبدئية ولا قيد في الكشف – أُضيفا ويحتاجان تأكيد.</t>
+          <t>2) عصمت: عقدان WHT-2756 و WHT-2758 (16,810.00) موجودان في سجل العقود فقط، بدون فاتورة مبدئية ولا قيد في الكشف – تمت إضافتهما.</t>
         </is>
       </c>
     </row>
@@ -726,14 +726,14 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>4) عصمت: WHT-1908 (16,658.75) بتاريخ 30-7-2025 وأبو خالد: WHK-1909 (11,570.00) بتاريخ 30-7-2025 – خارج الفترة بيوم واحد فاستُبعدا (موضحان بالرمادي).</t>
+          <t>4) العقدان WHT-1908 (16,658.75) و WHK-1909 (11,570.00) بتاريخ 30-7-2025 (قبل بداية الفترة بيوم) – أُدرجا بناءً على طلبك.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>5) أبو خالد (WHK): عقد عرعر WHK-2364 أدرجه المحاسب بقيمة العقد كاملة 440,000 بينما المسلّم والمسجل بالكشف 367,803.75 – تم اعتماد المسلّم.</t>
+          <t>5) أبو خالد (WHK): عقد عرعر WHK-2364 أُدرج بالقيمة الكاملة 440,000 بناءً على طلبك، علماً بأن المسجل بكشف الحساب 367,803.75 (الفرق 72,196.25 بدون قيد بالكشف).</t>
         </is>
       </c>
     </row>
@@ -754,26 +754,19 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>8) مبيعات السيارات: السيارة 1219 = عصمت، والسيارة 3010 = عماد. إجمالي المحاسب للسيارة 1219 (38,733.08) لم يخصم 3 فواتير مرتجعة بالكامل (4,123.90) فالصافي 34,609.18.</t>
+          <t>8) مبيعات السيارات: السيارة 1219 = عصمت، والسيارة 3010 = عماد. إجمالي المحاسب للسيارة 1219 (38,733.08) لم يخصم 3 فواتير مرتجعة بالكامل (4,123.90) فالصافي 34,609.18. شيت المرتجعات فيه صفّان مكرران (WS-RET-0002 و 0003).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>9) مبيعات السيارات تشمل ضريبة 15% بينما مبيعات الجملة بدون ضريبة. شيت المرتجعات فيه صفّان مكرران (WS-RET-0002 و 0003).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>10) بعض التواريخ في ملفات المحاسب مقلوبة (يوم/شهر) مثل 2026-11-07 وهي 7-11 أي 11 يوليو – تم تصحيحها.</t>
+          <t>9) بعض التواريخ في ملفات المحاسب مقلوبة (يوم/شهر) مثل 2026-11-07 وهي 7-11 أي 11 يوليو – تم تصحيحها.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="13">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A1:G1"/>
@@ -781,7 +774,6 @@
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A15:G15"/>
@@ -870,11 +862,11 @@
         <v>16658.75</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>0</v>
+        <v>16658.75</v>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>خارج الفترة</t>
+          <t>صحيح (ملاحظة)</t>
         </is>
       </c>
       <c r="G2" s="9" t="inlineStr">
@@ -884,7 +876,7 @@
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>تاريخه 2025-07-30 قبل بداية الفترة 31-7-2025</t>
+          <t>تاريخه 2025-07-30 قبل بداية الفترة 31-7-2025 بيوم – أُدرج بناءً على طلبك</t>
         </is>
       </c>
     </row>
@@ -8764,11 +8756,11 @@
         <v>11570</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>0</v>
+        <v>11570</v>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>خارج الفترة</t>
+          <t>صحيح (ملاحظة)</t>
         </is>
       </c>
       <c r="G2" s="9" t="inlineStr">
@@ -8778,7 +8770,7 @@
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>تاريخه 2025-07-30 قبل بداية الفترة 31-7-2025</t>
+          <t>تاريخه 2025-07-30 قبل بداية الفترة 31-7-2025 بيوم – أُدرج بناءً على طلبك</t>
         </is>
       </c>
     </row>
@@ -8903,36 +8895,36 @@
       <c r="H6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="10" t="n">
         <v>45935</v>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>WHK-2364</t>
         </is>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="11" t="n">
         <v>440000</v>
       </c>
-      <c r="E7" s="21" t="n">
-        <v>367803.75</v>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>معدّل</t>
-        </is>
-      </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="E7" s="11" t="n">
+        <v>440000</v>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>صحيح (ملاحظة)</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>كشف الحساب</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
-        <is>
-          <t>عقد عرعر: المحاسب أدرج قيمة العقد كاملة 440,000.00، والمسلّم فعلياً حسب كشف الحساب (7 قيود) 367,803.75 – الفرق 72,196.25 بدون مستند تسليم</t>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>عقد عرعر – أُدرج بالقيمة الكاملة 440,000.00 بناءً على طلبك. المسجل بكشف الحساب (7 قيود) 367,803.75 – الفرق 72,196.25 بدون قيد بالكشف</t>
         </is>
       </c>
     </row>
@@ -10202,7 +10194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10210,12 +10202,10 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10246,30 +10236,20 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>قبل الضريبة</t>
+          <t>قيمة الفاتورة</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>الضريبة 15%</t>
+          <t>الحالة</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>الإجمالي</t>
+          <t>الصافي بعد المرتجع</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>الحالة</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>صافي بعد المرتجع</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>الشهر</t>
         </is>
@@ -10300,24 +10280,18 @@
         </is>
       </c>
       <c r="F2" s="4" t="n">
-        <v>296.09</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>44.41</v>
+        <v>340.5</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H2" s="4" t="n">
         <v>340.5</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>340.5</v>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -10347,24 +10321,18 @@
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1856.52</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>278.48</v>
+        <v>2135</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H3" s="4" t="n">
         <v>2135</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>2135</v>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -10394,24 +10362,18 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>13.7</v>
+        <v>105</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H4" s="4" t="n">
         <v>105</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -10441,24 +10403,18 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>269.57</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>40.43</v>
+        <v>310</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H5" s="4" t="n">
         <v>310</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>310</v>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -10488,24 +10444,18 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1745.65</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>261.85</v>
+        <v>2007.5</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H6" s="4" t="n">
         <v>2007.5</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>2007.5</v>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -10535,24 +10485,18 @@
         </is>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1956.52</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>293.48</v>
+        <v>2250</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H7" s="4" t="n">
         <v>2250</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>2250</v>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -10582,24 +10526,18 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1710.43</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>256.57</v>
+        <v>1967</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H8" s="4" t="n">
         <v>1967</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>1967</v>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -10629,24 +10567,18 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2008.7</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>301.3</v>
+        <v>2310</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H9" s="4" t="n">
         <v>2310</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>2310</v>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -10676,24 +10608,18 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>828.26</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>124.24</v>
+        <v>952.5</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H10" s="4" t="n">
         <v>952.5</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>952.5</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -10723,24 +10649,18 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>666.96</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>100.04</v>
+        <v>767</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H11" s="4" t="n">
         <v>767</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>767</v>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -10770,24 +10690,18 @@
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1014.78</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>152.22</v>
+        <v>1167</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H12" s="4" t="n">
         <v>1167</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>1167</v>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -10817,23 +10731,17 @@
         </is>
       </c>
       <c r="F13" s="21" t="n">
-        <v>1468</v>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>220.2</v>
+        <v>1688.2</v>
+      </c>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>مرتجع بالكامل</t>
+        </is>
       </c>
       <c r="H13" s="21" t="n">
-        <v>1688.2</v>
+        <v>0</v>
       </c>
       <c r="I13" s="19" t="inlineStr">
-        <is>
-          <t>مرتجع بالكامل</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="19" t="inlineStr">
         <is>
           <t>6-2026</t>
         </is>
@@ -10864,23 +10772,17 @@
         </is>
       </c>
       <c r="F14" s="21" t="n">
-        <v>1468</v>
-      </c>
-      <c r="G14" s="21" t="n">
-        <v>220.2</v>
+        <v>1688.2</v>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>مرتجع بالكامل</t>
+        </is>
       </c>
       <c r="H14" s="21" t="n">
-        <v>1688.2</v>
+        <v>0</v>
       </c>
       <c r="I14" s="19" t="inlineStr">
-        <is>
-          <t>مرتجع بالكامل</t>
-        </is>
-      </c>
-      <c r="J14" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="19" t="inlineStr">
         <is>
           <t>6-2026</t>
         </is>
@@ -10911,24 +10813,18 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>560.87</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>84.13</v>
+        <v>645</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H15" s="4" t="n">
         <v>645</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>645</v>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -10958,23 +10854,17 @@
         </is>
       </c>
       <c r="F16" s="21" t="n">
-        <v>650</v>
-      </c>
-      <c r="G16" s="21" t="n">
-        <v>97.5</v>
+        <v>747.5</v>
+      </c>
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>مرتجع بالكامل</t>
+        </is>
       </c>
       <c r="H16" s="21" t="n">
-        <v>747.5</v>
+        <v>0</v>
       </c>
       <c r="I16" s="19" t="inlineStr">
-        <is>
-          <t>مرتجع بالكامل</t>
-        </is>
-      </c>
-      <c r="J16" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="19" t="inlineStr">
         <is>
           <t>6-2026</t>
         </is>
@@ -11005,24 +10895,18 @@
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1213.04</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>181.96</v>
+        <v>1395</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H17" s="4" t="n">
         <v>1395</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>1395</v>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -11052,24 +10936,18 @@
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>365.49</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>54.82</v>
+        <v>420.3125</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H18" s="4" t="n">
         <v>420.3125</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>420.3125</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -11099,24 +10977,18 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>222.17</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>33.33</v>
+        <v>255.5</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H19" s="4" t="n">
         <v>255.5</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>255.5</v>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -11146,24 +11018,18 @@
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>647.86</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>97.18000000000001</v>
+        <v>745.04375</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H20" s="4" t="n">
         <v>745.04375</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>745.04375</v>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -11193,24 +11059,18 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>852.83</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>127.92</v>
+        <v>980.75</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H21" s="4" t="n">
         <v>980.75</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>980.75</v>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -11240,24 +11100,18 @@
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>387.02</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>58.05</v>
+        <v>445.06875</v>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H22" s="4" t="n">
         <v>445.06875</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>445.06875</v>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -11287,24 +11141,18 @@
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1356.52</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>203.48</v>
+        <v>1560</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H23" s="4" t="n">
         <v>1560</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>1560</v>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -11334,24 +11182,18 @@
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>993.91</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>149.09</v>
+        <v>1143</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H24" s="4" t="n">
         <v>1143</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>1143</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -11381,24 +11223,18 @@
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>539.13</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>80.87</v>
+        <v>620</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H25" s="4" t="n">
         <v>620</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>620</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -11428,24 +11264,18 @@
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1152.17</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>172.83</v>
+        <v>1325</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H26" s="4" t="n">
         <v>1325</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>1325</v>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -11475,24 +11305,18 @@
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1082.61</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>162.39</v>
+        <v>1245</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H27" s="4" t="n">
         <v>1245</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>1245</v>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -11522,24 +11346,18 @@
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1473.91</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>221.09</v>
+        <v>1695</v>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H28" s="4" t="n">
         <v>1695</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>1695</v>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -11569,24 +11387,18 @@
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>130.43</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>19.57</v>
+        <v>150</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H29" s="4" t="n">
         <v>150</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -11616,24 +11428,18 @@
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>930.4299999999999</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>139.57</v>
+        <v>1070</v>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H30" s="4" t="n">
         <v>1070</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>1070</v>
-      </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -11663,24 +11469,18 @@
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>668.7</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>100.3</v>
+        <v>769</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H31" s="4" t="n">
         <v>769</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>769</v>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -11710,24 +11510,18 @@
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>139.13</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>20.87</v>
+        <v>160</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H32" s="4" t="n">
         <v>160</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -11757,24 +11551,18 @@
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>347.83</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>52.17</v>
+        <v>400</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H33" s="4" t="n">
         <v>400</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>400</v>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -11804,24 +11592,18 @@
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>547.83</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>82.17</v>
+        <v>630</v>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H34" s="4" t="n">
         <v>630</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>630</v>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -11851,24 +11633,18 @@
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>513.04</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>76.95999999999999</v>
+        <v>590</v>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H35" s="4" t="n">
         <v>590</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>590</v>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -11898,24 +11674,18 @@
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>469.57</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>70.43000000000001</v>
+        <v>540</v>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H36" s="4" t="n">
         <v>540</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="n">
-        <v>540</v>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -11945,24 +11715,18 @@
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>260.87</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>39.13</v>
+        <v>300</v>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H37" s="4" t="n">
         <v>300</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="K37" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -11992,24 +11756,18 @@
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>734.78</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>110.22</v>
+        <v>845</v>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H38" s="4" t="n">
         <v>845</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>845</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -12039,24 +11797,18 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>277.39</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>41.61</v>
+        <v>319</v>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H39" s="4" t="n">
         <v>319</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>319</v>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -12086,24 +11838,18 @@
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>572.17</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>85.83</v>
+        <v>658</v>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H40" s="4" t="n">
         <v>658</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="n">
-        <v>658</v>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -12133,24 +11879,18 @@
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>240.87</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>36.13</v>
+        <v>277</v>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H41" s="4" t="n">
         <v>277</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>277</v>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -12180,24 +11920,18 @@
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>195.65</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>29.35</v>
+        <v>225</v>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H42" s="4" t="n">
         <v>225</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>225</v>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -12227,24 +11961,18 @@
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>382.61</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>57.39</v>
+        <v>440</v>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H43" s="4" t="n">
         <v>440</v>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="n">
-        <v>440</v>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -12274,24 +12002,18 @@
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>391.3</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>58.7</v>
+        <v>450</v>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H44" s="4" t="n">
         <v>450</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="n">
-        <v>450</v>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -12321,24 +12043,18 @@
         </is>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1786.74</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>268.01</v>
+        <v>2054.75</v>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H45" s="4" t="n">
         <v>2054.75</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="n">
-        <v>2054.75</v>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
           <t>6-2026</t>
         </is>
       </c>
@@ -12368,24 +12084,18 @@
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1560.87</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>234.13</v>
+        <v>1795</v>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H46" s="4" t="n">
         <v>1795</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>1795</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -12415,24 +12125,18 @@
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>647.83</v>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>97.17</v>
+        <v>745</v>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H47" s="4" t="n">
         <v>745</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="n">
-        <v>745</v>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -12462,24 +12166,18 @@
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>256.52</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>38.48</v>
+        <v>295</v>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H48" s="4" t="n">
         <v>295</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="n">
-        <v>295</v>
-      </c>
-      <c r="K48" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -12509,24 +12207,18 @@
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>247.83</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>37.17</v>
+        <v>285</v>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H49" s="4" t="n">
         <v>285</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="n">
-        <v>285</v>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -12556,24 +12248,18 @@
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>126.09</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>18.91</v>
+        <v>145</v>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H50" s="4" t="n">
         <v>145</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J50" s="4" t="n">
-        <v>145</v>
-      </c>
-      <c r="K50" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -12603,24 +12289,18 @@
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>234.78</v>
-      </c>
-      <c r="G51" s="4" t="n">
-        <v>35.22</v>
+        <v>270</v>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H51" s="4" t="n">
         <v>270</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="n">
-        <v>270</v>
-      </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -12650,24 +12330,18 @@
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>130.43</v>
-      </c>
-      <c r="G52" s="4" t="n">
-        <v>19.57</v>
+        <v>150</v>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H52" s="4" t="n">
         <v>150</v>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="K52" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -12697,24 +12371,18 @@
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>108.7</v>
-      </c>
-      <c r="G53" s="4" t="n">
-        <v>16.3</v>
+        <v>125</v>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H53" s="4" t="n">
         <v>125</v>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="K53" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -12744,24 +12412,18 @@
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>108.7</v>
-      </c>
-      <c r="G54" s="4" t="n">
-        <v>16.3</v>
+        <v>125</v>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H54" s="4" t="n">
         <v>125</v>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J54" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -12791,24 +12453,18 @@
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>234.78</v>
-      </c>
-      <c r="G55" s="4" t="n">
-        <v>35.22</v>
+        <v>270</v>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H55" s="4" t="n">
         <v>270</v>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="n">
-        <v>270</v>
-      </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -12838,24 +12494,18 @@
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>108.7</v>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>16.3</v>
+        <v>125</v>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H56" s="4" t="n">
         <v>125</v>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J56" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="K56" s="3" t="inlineStr">
-        <is>
           <t>7-2026</t>
         </is>
       </c>
@@ -12885,23 +12535,17 @@
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>65.22</v>
-      </c>
-      <c r="G57" s="4" t="n">
-        <v>9.779999999999999</v>
+        <v>75</v>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>مكتمل</t>
+        </is>
       </c>
       <c r="H57" s="4" t="n">
         <v>75</v>
       </c>
       <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>مكتمل</t>
-        </is>
-      </c>
-      <c r="J57" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="K57" s="3" t="inlineStr">
         <is>
           <t>7-2026</t>
         </is>
@@ -12921,20 +12565,12 @@
         <f>SUM(F2:F57)</f>
         <v/>
       </c>
-      <c r="G58" s="6">
-        <f>SUM(G2:G57)</f>
-        <v/>
-      </c>
+      <c r="G58" s="5" t="inlineStr"/>
       <c r="H58" s="6">
         <f>SUM(H2:H57)</f>
         <v/>
       </c>
-      <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="6">
-        <f>SUM(J2:J57)</f>
-        <v/>
-      </c>
-      <c r="K58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/إجمالي_مبيعات_المناديب_31-7-2025_إلى_31-7-2026.xlsx
+++ b/إجمالي_مبيعات_المناديب_31-7-2025_إلى_31-7-2026.xlsx
@@ -11,7 +11,8 @@
     <sheet name="عصمت - جملة WHT" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="عماد - جملة WHE" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="أبو خالد - جملة WHK" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="مبيعات السيارات 6-7 2026" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="أبو خالد - تفصيل البنود" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="مبيعات السيارات 6-7 2026" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'عصمت - جملة WHT'!$A$1:$H$212</definedName>
@@ -25,8 +26,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -48,7 +49,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +86,11 @@
         <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -112,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -129,18 +135,34 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -850,7 +872,7 @@
       <c r="A2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="n">
+      <c r="B2" s="22" t="n">
         <v>45868</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
@@ -884,7 +906,7 @@
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="23" t="n">
         <v>45878</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -914,7 +936,7 @@
       <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="23" t="n">
         <v>45885</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -944,7 +966,7 @@
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="23" t="n">
         <v>45885</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -974,7 +996,7 @@
       <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="23" t="n">
         <v>45887</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1004,7 +1026,7 @@
       <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="23" t="n">
         <v>45889</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1034,7 +1056,7 @@
       <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="23" t="n">
         <v>45890</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1064,7 +1086,7 @@
       <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="23" t="n">
         <v>45892</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1094,7 +1116,7 @@
       <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="23" t="n">
         <v>45894</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -1124,7 +1146,7 @@
       <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="23" t="n">
         <v>45895</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1154,7 +1176,7 @@
       <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="23" t="n">
         <v>45897</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -1184,7 +1206,7 @@
       <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="23" t="n">
         <v>45901</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1214,7 +1236,7 @@
       <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="23" t="n">
         <v>45904</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1244,7 +1266,7 @@
       <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="23" t="n">
         <v>45907</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1274,7 +1296,7 @@
       <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="23" t="n">
         <v>45908</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1304,7 +1326,7 @@
       <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="23" t="n">
         <v>45909</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1334,7 +1356,7 @@
       <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="23" t="n">
         <v>45911</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1364,7 +1386,7 @@
       <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="23" t="n">
         <v>45915</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1394,7 +1416,7 @@
       <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="23" t="n">
         <v>45915</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1424,7 +1446,7 @@
       <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="23" t="n">
         <v>45916</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1454,7 +1476,7 @@
       <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="23" t="n">
         <v>45917</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1484,7 +1506,7 @@
       <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="12" t="n">
+      <c r="B23" s="23" t="n">
         <v>45918</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1514,7 +1536,7 @@
       <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="23" t="n">
         <v>45920</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1544,7 +1566,7 @@
       <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="23" t="n">
         <v>45921</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1574,7 +1596,7 @@
       <c r="A26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="23" t="n">
         <v>45922</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1604,7 +1626,7 @@
       <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="12" t="n">
+      <c r="B27" s="23" t="n">
         <v>45924</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1634,7 +1656,7 @@
       <c r="A28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="23" t="n">
         <v>45925</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1664,7 +1686,7 @@
       <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="23" t="n">
         <v>45926</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1694,7 +1716,7 @@
       <c r="A30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="23" t="n">
         <v>45930</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1724,7 +1746,7 @@
       <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="12" t="n">
+      <c r="B31" s="23" t="n">
         <v>45930</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -1754,7 +1776,7 @@
       <c r="A32" s="13" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="14" t="n">
+      <c r="B32" s="24" t="n">
         <v>45931</v>
       </c>
       <c r="C32" s="13" t="inlineStr">
@@ -1788,7 +1810,7 @@
       <c r="A33" s="13" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="14" t="n">
+      <c r="B33" s="24" t="n">
         <v>45932</v>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -1822,7 +1844,7 @@
       <c r="A34" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="14" t="n">
+      <c r="B34" s="24" t="n">
         <v>45934</v>
       </c>
       <c r="C34" s="13" t="inlineStr">
@@ -1856,7 +1878,7 @@
       <c r="A35" s="13" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="14" t="n">
+      <c r="B35" s="24" t="n">
         <v>45935</v>
       </c>
       <c r="C35" s="13" t="inlineStr">
@@ -1890,7 +1912,7 @@
       <c r="A36" s="13" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="14" t="n">
+      <c r="B36" s="24" t="n">
         <v>45936</v>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -1924,7 +1946,7 @@
       <c r="A37" s="13" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="14" t="n">
+      <c r="B37" s="24" t="n">
         <v>45938</v>
       </c>
       <c r="C37" s="13" t="inlineStr">
@@ -1958,7 +1980,7 @@
       <c r="A38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="12" t="n">
+      <c r="B38" s="23" t="n">
         <v>45939</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -1988,7 +2010,7 @@
       <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="23" t="n">
         <v>45941</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2018,7 +2040,7 @@
       <c r="A40" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="12" t="n">
+      <c r="B40" s="23" t="n">
         <v>45942</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2048,7 +2070,7 @@
       <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="12" t="n">
+      <c r="B41" s="23" t="n">
         <v>45943</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2078,7 +2100,7 @@
       <c r="A42" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="12" t="n">
+      <c r="B42" s="23" t="n">
         <v>45944</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2108,7 +2130,7 @@
       <c r="A43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B43" s="23" t="n">
         <v>45945</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2138,7 +2160,7 @@
       <c r="A44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="12" t="n">
+      <c r="B44" s="23" t="n">
         <v>45946</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2168,7 +2190,7 @@
       <c r="A45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="12" t="n">
+      <c r="B45" s="23" t="n">
         <v>45949</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2198,7 +2220,7 @@
       <c r="A46" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="12" t="n">
+      <c r="B46" s="23" t="n">
         <v>45950</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -2228,7 +2250,7 @@
       <c r="A47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="12" t="n">
+      <c r="B47" s="23" t="n">
         <v>45951</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -2258,7 +2280,7 @@
       <c r="A48" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="12" t="n">
+      <c r="B48" s="23" t="n">
         <v>45952</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -2288,7 +2310,7 @@
       <c r="A49" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="12" t="n">
+      <c r="B49" s="23" t="n">
         <v>45953</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -2318,7 +2340,7 @@
       <c r="A50" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="12" t="n">
+      <c r="B50" s="23" t="n">
         <v>45955</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -2348,7 +2370,7 @@
       <c r="A51" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="12" t="n">
+      <c r="B51" s="23" t="n">
         <v>45956</v>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -2378,7 +2400,7 @@
       <c r="A52" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="12" t="n">
+      <c r="B52" s="23" t="n">
         <v>45957</v>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -2408,7 +2430,7 @@
       <c r="A53" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="12" t="n">
+      <c r="B53" s="23" t="n">
         <v>45958</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -2438,7 +2460,7 @@
       <c r="A54" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="12" t="n">
+      <c r="B54" s="23" t="n">
         <v>45959</v>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -2468,7 +2490,7 @@
       <c r="A55" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="12" t="n">
+      <c r="B55" s="23" t="n">
         <v>45960</v>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -2498,7 +2520,7 @@
       <c r="A56" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="12" t="n">
+      <c r="B56" s="23" t="n">
         <v>45962</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -2528,7 +2550,7 @@
       <c r="A57" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="12" t="n">
+      <c r="B57" s="23" t="n">
         <v>45963</v>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -2558,7 +2580,7 @@
       <c r="A58" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="12" t="n">
+      <c r="B58" s="23" t="n">
         <v>45964</v>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -2588,7 +2610,7 @@
       <c r="A59" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="12" t="n">
+      <c r="B59" s="23" t="n">
         <v>45966</v>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -2618,7 +2640,7 @@
       <c r="A60" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="12" t="n">
+      <c r="B60" s="23" t="n">
         <v>45967</v>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -2648,7 +2670,7 @@
       <c r="A61" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="12" t="n">
+      <c r="B61" s="23" t="n">
         <v>45969</v>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -2678,7 +2700,7 @@
       <c r="A62" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="12" t="n">
+      <c r="B62" s="23" t="n">
         <v>45970</v>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -2708,7 +2730,7 @@
       <c r="A63" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="12" t="n">
+      <c r="B63" s="23" t="n">
         <v>45971</v>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -2738,7 +2760,7 @@
       <c r="A64" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="12" t="n">
+      <c r="B64" s="23" t="n">
         <v>45973</v>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -2768,7 +2790,7 @@
       <c r="A65" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="12" t="n">
+      <c r="B65" s="23" t="n">
         <v>45974</v>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -2798,7 +2820,7 @@
       <c r="A66" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="12" t="n">
+      <c r="B66" s="23" t="n">
         <v>45977</v>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -2828,7 +2850,7 @@
       <c r="A67" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="12" t="n">
+      <c r="B67" s="23" t="n">
         <v>45978</v>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -2858,7 +2880,7 @@
       <c r="A68" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="12" t="n">
+      <c r="B68" s="23" t="n">
         <v>45979</v>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -2888,7 +2910,7 @@
       <c r="A69" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="12" t="n">
+      <c r="B69" s="23" t="n">
         <v>45980</v>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -2918,7 +2940,7 @@
       <c r="A70" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="12" t="n">
+      <c r="B70" s="23" t="n">
         <v>45981</v>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -2948,7 +2970,7 @@
       <c r="A71" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="12" t="n">
+      <c r="B71" s="23" t="n">
         <v>45983</v>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -2978,7 +3000,7 @@
       <c r="A72" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="12" t="n">
+      <c r="B72" s="23" t="n">
         <v>45984</v>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -3008,7 +3030,7 @@
       <c r="A73" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="12" t="n">
+      <c r="B73" s="23" t="n">
         <v>45985</v>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -3038,7 +3060,7 @@
       <c r="A74" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="12" t="n">
+      <c r="B74" s="23" t="n">
         <v>45986</v>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -3068,7 +3090,7 @@
       <c r="A75" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="12" t="n">
+      <c r="B75" s="23" t="n">
         <v>45988</v>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -3098,7 +3120,7 @@
       <c r="A76" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="12" t="n">
+      <c r="B76" s="23" t="n">
         <v>45990</v>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -3128,7 +3150,7 @@
       <c r="A77" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="12" t="n">
+      <c r="B77" s="23" t="n">
         <v>45991</v>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -3158,7 +3180,7 @@
       <c r="A78" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="12" t="n">
+      <c r="B78" s="23" t="n">
         <v>45992</v>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -3188,7 +3210,7 @@
       <c r="A79" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="12" t="n">
+      <c r="B79" s="23" t="n">
         <v>45993</v>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -3218,7 +3240,7 @@
       <c r="A80" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="12" t="n">
+      <c r="B80" s="23" t="n">
         <v>45994</v>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -3248,7 +3270,7 @@
       <c r="A81" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="12" t="n">
+      <c r="B81" s="23" t="n">
         <v>45995</v>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -3278,7 +3300,7 @@
       <c r="A82" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="12" t="n">
+      <c r="B82" s="23" t="n">
         <v>45997</v>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -3308,7 +3330,7 @@
       <c r="A83" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="12" t="n">
+      <c r="B83" s="23" t="n">
         <v>45998</v>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -3338,7 +3360,7 @@
       <c r="A84" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="12" t="n">
+      <c r="B84" s="23" t="n">
         <v>45999</v>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -3368,7 +3390,7 @@
       <c r="A85" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="12" t="n">
+      <c r="B85" s="23" t="n">
         <v>46000</v>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -3398,7 +3420,7 @@
       <c r="A86" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="12" t="n">
+      <c r="B86" s="23" t="n">
         <v>46001</v>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -3428,7 +3450,7 @@
       <c r="A87" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="12" t="n">
+      <c r="B87" s="23" t="n">
         <v>46002</v>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -3458,7 +3480,7 @@
       <c r="A88" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="12" t="n">
+      <c r="B88" s="23" t="n">
         <v>46004</v>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -3488,7 +3510,7 @@
       <c r="A89" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="12" t="n">
+      <c r="B89" s="23" t="n">
         <v>46005</v>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -3518,7 +3540,7 @@
       <c r="A90" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="12" t="n">
+      <c r="B90" s="23" t="n">
         <v>46006</v>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -3548,7 +3570,7 @@
       <c r="A91" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="12" t="n">
+      <c r="B91" s="23" t="n">
         <v>46007</v>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -3578,7 +3600,7 @@
       <c r="A92" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="12" t="n">
+      <c r="B92" s="23" t="n">
         <v>46008</v>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -3608,7 +3630,7 @@
       <c r="A93" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="12" t="n">
+      <c r="B93" s="23" t="n">
         <v>46011</v>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -3638,7 +3660,7 @@
       <c r="A94" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="12" t="n">
+      <c r="B94" s="23" t="n">
         <v>46012</v>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -3668,7 +3690,7 @@
       <c r="A95" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="12" t="n">
+      <c r="B95" s="23" t="n">
         <v>46013</v>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -3698,7 +3720,7 @@
       <c r="A96" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="12" t="n">
+      <c r="B96" s="23" t="n">
         <v>46014</v>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -3728,7 +3750,7 @@
       <c r="A97" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="12" t="n">
+      <c r="B97" s="23" t="n">
         <v>46015</v>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -3758,7 +3780,7 @@
       <c r="A98" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="12" t="n">
+      <c r="B98" s="23" t="n">
         <v>46016</v>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -3788,7 +3810,7 @@
       <c r="A99" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="12" t="n">
+      <c r="B99" s="23" t="n">
         <v>46018</v>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -3818,7 +3840,7 @@
       <c r="A100" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="12" t="n">
+      <c r="B100" s="23" t="n">
         <v>46019</v>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -3848,7 +3870,7 @@
       <c r="A101" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="12" t="n">
+      <c r="B101" s="23" t="n">
         <v>46020</v>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -3878,7 +3900,7 @@
       <c r="A102" s="3" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="12" t="n">
+      <c r="B102" s="23" t="n">
         <v>46021</v>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -3908,7 +3930,7 @@
       <c r="A103" s="3" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="12" t="n">
+      <c r="B103" s="23" t="n">
         <v>46023</v>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -3938,7 +3960,7 @@
       <c r="A104" s="3" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="12" t="n">
+      <c r="B104" s="23" t="n">
         <v>46025</v>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -3968,7 +3990,7 @@
       <c r="A105" s="3" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="12" t="n">
+      <c r="B105" s="23" t="n">
         <v>46026</v>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -3998,7 +4020,7 @@
       <c r="A106" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="12" t="n">
+      <c r="B106" s="23" t="n">
         <v>46027</v>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -4028,7 +4050,7 @@
       <c r="A107" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="12" t="n">
+      <c r="B107" s="23" t="n">
         <v>46028</v>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -4058,7 +4080,7 @@
       <c r="A108" s="3" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="12" t="n">
+      <c r="B108" s="23" t="n">
         <v>46029</v>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -4088,7 +4110,7 @@
       <c r="A109" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="12" t="n">
+      <c r="B109" s="23" t="n">
         <v>46030</v>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -4118,7 +4140,7 @@
       <c r="A110" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="12" t="n">
+      <c r="B110" s="23" t="n">
         <v>46032</v>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -4148,7 +4170,7 @@
       <c r="A111" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="12" t="n">
+      <c r="B111" s="23" t="n">
         <v>46034</v>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -4178,7 +4200,7 @@
       <c r="A112" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="12" t="n">
+      <c r="B112" s="23" t="n">
         <v>46035</v>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -4208,7 +4230,7 @@
       <c r="A113" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="12" t="n">
+      <c r="B113" s="23" t="n">
         <v>46036</v>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -4238,7 +4260,7 @@
       <c r="A114" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="12" t="n">
+      <c r="B114" s="23" t="n">
         <v>46037</v>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -4268,7 +4290,7 @@
       <c r="A115" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="12" t="n">
+      <c r="B115" s="23" t="n">
         <v>46039</v>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -4298,7 +4320,7 @@
       <c r="A116" s="3" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="12" t="n">
+      <c r="B116" s="23" t="n">
         <v>46040</v>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -4328,7 +4350,7 @@
       <c r="A117" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="12" t="n">
+      <c r="B117" s="23" t="n">
         <v>46041</v>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -4358,7 +4380,7 @@
       <c r="A118" s="3" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="12" t="n">
+      <c r="B118" s="23" t="n">
         <v>46044</v>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -4388,7 +4410,7 @@
       <c r="A119" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="12" t="n">
+      <c r="B119" s="23" t="n">
         <v>46046</v>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -4418,7 +4440,7 @@
       <c r="A120" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="12" t="n">
+      <c r="B120" s="23" t="n">
         <v>46047</v>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -4448,7 +4470,7 @@
       <c r="A121" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="12" t="n">
+      <c r="B121" s="23" t="n">
         <v>46048</v>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -4478,7 +4500,7 @@
       <c r="A122" s="3" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="12" t="n">
+      <c r="B122" s="23" t="n">
         <v>46049</v>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -4508,7 +4530,7 @@
       <c r="A123" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="12" t="n">
+      <c r="B123" s="23" t="n">
         <v>46050</v>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -4538,7 +4560,7 @@
       <c r="A124" s="3" t="n">
         <v>123</v>
       </c>
-      <c r="B124" s="12" t="n">
+      <c r="B124" s="23" t="n">
         <v>46051</v>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -4568,7 +4590,7 @@
       <c r="A125" s="3" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="12" t="n">
+      <c r="B125" s="23" t="n">
         <v>46053</v>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -4598,7 +4620,7 @@
       <c r="A126" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="B126" s="12" t="n">
+      <c r="B126" s="23" t="n">
         <v>46054</v>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -4628,7 +4650,7 @@
       <c r="A127" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="B127" s="12" t="n">
+      <c r="B127" s="23" t="n">
         <v>46055</v>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -4658,7 +4680,7 @@
       <c r="A128" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="B128" s="12" t="n">
+      <c r="B128" s="23" t="n">
         <v>46056</v>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -4688,7 +4710,7 @@
       <c r="A129" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="12" t="n">
+      <c r="B129" s="23" t="n">
         <v>46057</v>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -4718,7 +4740,7 @@
       <c r="A130" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="12" t="n">
+      <c r="B130" s="23" t="n">
         <v>46058</v>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -4748,7 +4770,7 @@
       <c r="A131" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="12" t="n">
+      <c r="B131" s="23" t="n">
         <v>46060</v>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -4778,7 +4800,7 @@
       <c r="A132" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="12" t="n">
+      <c r="B132" s="23" t="n">
         <v>46061</v>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -4808,7 +4830,7 @@
       <c r="A133" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="12" t="n">
+      <c r="B133" s="23" t="n">
         <v>46062</v>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -4838,7 +4860,7 @@
       <c r="A134" s="16" t="n">
         <v>133</v>
       </c>
-      <c r="B134" s="17" t="n">
+      <c r="B134" s="25" t="n">
         <v>46063</v>
       </c>
       <c r="C134" s="16" t="inlineStr">
@@ -4872,7 +4894,7 @@
       <c r="A135" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="12" t="n">
+      <c r="B135" s="23" t="n">
         <v>46064</v>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -4902,7 +4924,7 @@
       <c r="A136" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="B136" s="12" t="n">
+      <c r="B136" s="23" t="n">
         <v>46065</v>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -4932,7 +4954,7 @@
       <c r="A137" s="3" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="12" t="n">
+      <c r="B137" s="23" t="n">
         <v>46067</v>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -4962,7 +4984,7 @@
       <c r="A138" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="B138" s="12" t="n">
+      <c r="B138" s="23" t="n">
         <v>46068</v>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -4992,7 +5014,7 @@
       <c r="A139" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="B139" s="12" t="n">
+      <c r="B139" s="23" t="n">
         <v>46069</v>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -5022,7 +5044,7 @@
       <c r="A140" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="12" t="n">
+      <c r="B140" s="23" t="n">
         <v>46070</v>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -5052,7 +5074,7 @@
       <c r="A141" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="B141" s="12" t="n">
+      <c r="B141" s="23" t="n">
         <v>46071</v>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -5082,7 +5104,7 @@
       <c r="A142" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="B142" s="12" t="n">
+      <c r="B142" s="23" t="n">
         <v>46073</v>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -5112,7 +5134,7 @@
       <c r="A143" s="3" t="n">
         <v>142</v>
       </c>
-      <c r="B143" s="12" t="n">
+      <c r="B143" s="23" t="n">
         <v>46074</v>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -5142,7 +5164,7 @@
       <c r="A144" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="B144" s="12" t="n">
+      <c r="B144" s="23" t="n">
         <v>46075</v>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -5172,7 +5194,7 @@
       <c r="A145" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="B145" s="12" t="n">
+      <c r="B145" s="23" t="n">
         <v>46076</v>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -5202,7 +5224,7 @@
       <c r="A146" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="B146" s="12" t="n">
+      <c r="B146" s="23" t="n">
         <v>46077</v>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -5232,7 +5254,7 @@
       <c r="A147" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="B147" s="12" t="n">
+      <c r="B147" s="23" t="n">
         <v>46078</v>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -5262,7 +5284,7 @@
       <c r="A148" s="3" t="n">
         <v>147</v>
       </c>
-      <c r="B148" s="12" t="n">
+      <c r="B148" s="23" t="n">
         <v>46081</v>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -5292,7 +5314,7 @@
       <c r="A149" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="B149" s="12" t="n">
+      <c r="B149" s="23" t="n">
         <v>46082</v>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -5322,7 +5344,7 @@
       <c r="A150" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="B150" s="12" t="n">
+      <c r="B150" s="23" t="n">
         <v>46083</v>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -5352,7 +5374,7 @@
       <c r="A151" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="B151" s="12" t="n">
+      <c r="B151" s="23" t="n">
         <v>46086</v>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -5382,7 +5404,7 @@
       <c r="A152" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="B152" s="12" t="n">
+      <c r="B152" s="23" t="n">
         <v>46088</v>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -5412,7 +5434,7 @@
       <c r="A153" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="B153" s="12" t="n">
+      <c r="B153" s="23" t="n">
         <v>46089</v>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -5442,7 +5464,7 @@
       <c r="A154" s="3" t="n">
         <v>153</v>
       </c>
-      <c r="B154" s="12" t="n">
+      <c r="B154" s="23" t="n">
         <v>46090</v>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -5472,7 +5494,7 @@
       <c r="A155" s="3" t="n">
         <v>154</v>
       </c>
-      <c r="B155" s="12" t="n">
+      <c r="B155" s="23" t="n">
         <v>46091</v>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -5502,7 +5524,7 @@
       <c r="A156" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="B156" s="12" t="n">
+      <c r="B156" s="23" t="n">
         <v>46092</v>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -5532,7 +5554,7 @@
       <c r="A157" s="3" t="n">
         <v>156</v>
       </c>
-      <c r="B157" s="12" t="n">
+      <c r="B157" s="23" t="n">
         <v>46093</v>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -5562,7 +5584,7 @@
       <c r="A158" s="3" t="n">
         <v>157</v>
       </c>
-      <c r="B158" s="12" t="n">
+      <c r="B158" s="23" t="n">
         <v>46094</v>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -5592,7 +5614,7 @@
       <c r="A159" s="3" t="n">
         <v>158</v>
       </c>
-      <c r="B159" s="12" t="n">
+      <c r="B159" s="23" t="n">
         <v>46095</v>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -5622,7 +5644,7 @@
       <c r="A160" s="3" t="n">
         <v>159</v>
       </c>
-      <c r="B160" s="12" t="n">
+      <c r="B160" s="23" t="n">
         <v>46096</v>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -5652,7 +5674,7 @@
       <c r="A161" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="B161" s="12" t="n">
+      <c r="B161" s="23" t="n">
         <v>46097</v>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -5682,7 +5704,7 @@
       <c r="A162" s="3" t="n">
         <v>161</v>
       </c>
-      <c r="B162" s="12" t="n">
+      <c r="B162" s="23" t="n">
         <v>46098</v>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -5712,7 +5734,7 @@
       <c r="A163" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="B163" s="12" t="n">
+      <c r="B163" s="23" t="n">
         <v>46100</v>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -5742,7 +5764,7 @@
       <c r="A164" s="16" t="n">
         <v>163</v>
       </c>
-      <c r="B164" s="17" t="n">
+      <c r="B164" s="25" t="n">
         <v>46106</v>
       </c>
       <c r="C164" s="16" t="inlineStr">
@@ -5776,7 +5798,7 @@
       <c r="A165" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="B165" s="12" t="n">
+      <c r="B165" s="23" t="n">
         <v>46107</v>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -5806,7 +5828,7 @@
       <c r="A166" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="B166" s="12" t="n">
+      <c r="B166" s="23" t="n">
         <v>46110</v>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -5836,7 +5858,7 @@
       <c r="A167" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="B167" s="12" t="n">
+      <c r="B167" s="23" t="n">
         <v>46111</v>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -5866,7 +5888,7 @@
       <c r="A168" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="B168" s="12" t="n">
+      <c r="B168" s="23" t="n">
         <v>46112</v>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -5896,7 +5918,7 @@
       <c r="A169" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="B169" s="12" t="n">
+      <c r="B169" s="23" t="n">
         <v>46113</v>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -5926,7 +5948,7 @@
       <c r="A170" s="3" t="n">
         <v>169</v>
       </c>
-      <c r="B170" s="12" t="n">
+      <c r="B170" s="23" t="n">
         <v>46114</v>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -5956,7 +5978,7 @@
       <c r="A171" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="B171" s="12" t="n">
+      <c r="B171" s="23" t="n">
         <v>46116</v>
       </c>
       <c r="C171" s="3" t="inlineStr">
@@ -5986,7 +6008,7 @@
       <c r="A172" s="3" t="n">
         <v>171</v>
       </c>
-      <c r="B172" s="12" t="n">
+      <c r="B172" s="23" t="n">
         <v>46117</v>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -6016,7 +6038,7 @@
       <c r="A173" s="3" t="n">
         <v>172</v>
       </c>
-      <c r="B173" s="12" t="n">
+      <c r="B173" s="23" t="n">
         <v>46118</v>
       </c>
       <c r="C173" s="3" t="inlineStr">
@@ -6046,7 +6068,7 @@
       <c r="A174" s="3" t="n">
         <v>173</v>
       </c>
-      <c r="B174" s="12" t="n">
+      <c r="B174" s="23" t="n">
         <v>46119</v>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -6076,7 +6098,7 @@
       <c r="A175" s="3" t="n">
         <v>174</v>
       </c>
-      <c r="B175" s="12" t="n">
+      <c r="B175" s="23" t="n">
         <v>46121</v>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -6106,7 +6128,7 @@
       <c r="A176" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="B176" s="12" t="n">
+      <c r="B176" s="23" t="n">
         <v>46123</v>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -6136,7 +6158,7 @@
       <c r="A177" s="3" t="n">
         <v>176</v>
       </c>
-      <c r="B177" s="12" t="n">
+      <c r="B177" s="23" t="n">
         <v>46127</v>
       </c>
       <c r="C177" s="3" t="inlineStr">
@@ -6166,7 +6188,7 @@
       <c r="A178" s="3" t="n">
         <v>177</v>
       </c>
-      <c r="B178" s="12" t="n">
+      <c r="B178" s="23" t="n">
         <v>46130</v>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -6196,7 +6218,7 @@
       <c r="A179" s="3" t="n">
         <v>178</v>
       </c>
-      <c r="B179" s="12" t="n">
+      <c r="B179" s="23" t="n">
         <v>46131</v>
       </c>
       <c r="C179" s="3" t="inlineStr">
@@ -6226,7 +6248,7 @@
       <c r="A180" s="3" t="n">
         <v>179</v>
       </c>
-      <c r="B180" s="12" t="n">
+      <c r="B180" s="23" t="n">
         <v>46132</v>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -6256,7 +6278,7 @@
       <c r="A181" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="B181" s="12" t="n">
+      <c r="B181" s="23" t="n">
         <v>46133</v>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -6286,7 +6308,7 @@
       <c r="A182" s="3" t="n">
         <v>181</v>
       </c>
-      <c r="B182" s="12" t="n">
+      <c r="B182" s="23" t="n">
         <v>46134</v>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -6316,7 +6338,7 @@
       <c r="A183" s="3" t="n">
         <v>182</v>
       </c>
-      <c r="B183" s="12" t="n">
+      <c r="B183" s="23" t="n">
         <v>46137</v>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -6346,7 +6368,7 @@
       <c r="A184" s="3" t="n">
         <v>183</v>
       </c>
-      <c r="B184" s="12" t="n">
+      <c r="B184" s="23" t="n">
         <v>46138</v>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -6376,7 +6398,7 @@
       <c r="A185" s="3" t="n">
         <v>184</v>
       </c>
-      <c r="B185" s="12" t="n">
+      <c r="B185" s="23" t="n">
         <v>46139</v>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -6406,7 +6428,7 @@
       <c r="A186" s="3" t="n">
         <v>185</v>
       </c>
-      <c r="B186" s="12" t="n">
+      <c r="B186" s="23" t="n">
         <v>46141</v>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -6436,7 +6458,7 @@
       <c r="A187" s="3" t="n">
         <v>186</v>
       </c>
-      <c r="B187" s="12" t="n">
+      <c r="B187" s="23" t="n">
         <v>46141</v>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -6466,7 +6488,7 @@
       <c r="A188" s="16" t="n">
         <v>187</v>
       </c>
-      <c r="B188" s="17" t="n">
+      <c r="B188" s="25" t="n">
         <v>46142</v>
       </c>
       <c r="C188" s="16" t="inlineStr">
@@ -6500,7 +6522,7 @@
       <c r="A189" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="B189" s="12" t="n">
+      <c r="B189" s="23" t="n">
         <v>46144</v>
       </c>
       <c r="C189" s="3" t="inlineStr">
@@ -6530,7 +6552,7 @@
       <c r="A190" s="3" t="n">
         <v>189</v>
       </c>
-      <c r="B190" s="12" t="n">
+      <c r="B190" s="23" t="n">
         <v>46145</v>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -6560,7 +6582,7 @@
       <c r="A191" s="3" t="n">
         <v>190</v>
       </c>
-      <c r="B191" s="12" t="n">
+      <c r="B191" s="23" t="n">
         <v>46146</v>
       </c>
       <c r="C191" s="3" t="inlineStr">
@@ -6590,7 +6612,7 @@
       <c r="A192" s="3" t="n">
         <v>191</v>
       </c>
-      <c r="B192" s="12" t="n">
+      <c r="B192" s="23" t="n">
         <v>46147</v>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -6620,7 +6642,7 @@
       <c r="A193" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="B193" s="12" t="n">
+      <c r="B193" s="23" t="n">
         <v>46148</v>
       </c>
       <c r="C193" s="3" t="inlineStr">
@@ -6650,7 +6672,7 @@
       <c r="A194" s="3" t="n">
         <v>193</v>
       </c>
-      <c r="B194" s="12" t="n">
+      <c r="B194" s="23" t="n">
         <v>46149</v>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -6680,7 +6702,7 @@
       <c r="A195" s="3" t="n">
         <v>194</v>
       </c>
-      <c r="B195" s="12" t="n">
+      <c r="B195" s="23" t="n">
         <v>46151</v>
       </c>
       <c r="C195" s="3" t="inlineStr">
@@ -6710,7 +6732,7 @@
       <c r="A196" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="B196" s="12" t="n">
+      <c r="B196" s="23" t="n">
         <v>46152</v>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -6740,7 +6762,7 @@
       <c r="A197" s="3" t="n">
         <v>196</v>
       </c>
-      <c r="B197" s="12" t="n">
+      <c r="B197" s="23" t="n">
         <v>46153</v>
       </c>
       <c r="C197" s="3" t="inlineStr">
@@ -6770,7 +6792,7 @@
       <c r="A198" s="3" t="n">
         <v>197</v>
       </c>
-      <c r="B198" s="12" t="n">
+      <c r="B198" s="23" t="n">
         <v>46154</v>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -6800,7 +6822,7 @@
       <c r="A199" s="3" t="n">
         <v>198</v>
       </c>
-      <c r="B199" s="12" t="n">
+      <c r="B199" s="23" t="n">
         <v>46155</v>
       </c>
       <c r="C199" s="3" t="inlineStr">
@@ -6830,7 +6852,7 @@
       <c r="A200" s="3" t="n">
         <v>199</v>
       </c>
-      <c r="B200" s="12" t="n">
+      <c r="B200" s="23" t="n">
         <v>46156</v>
       </c>
       <c r="C200" s="3" t="inlineStr">
@@ -6860,7 +6882,7 @@
       <c r="A201" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="B201" s="12" t="n">
+      <c r="B201" s="23" t="n">
         <v>46158</v>
       </c>
       <c r="C201" s="3" t="inlineStr">
@@ -6890,7 +6912,7 @@
       <c r="A202" s="3" t="n">
         <v>201</v>
       </c>
-      <c r="B202" s="12" t="n">
+      <c r="B202" s="23" t="n">
         <v>46159</v>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -6920,7 +6942,7 @@
       <c r="A203" s="3" t="n">
         <v>202</v>
       </c>
-      <c r="B203" s="12" t="n">
+      <c r="B203" s="23" t="n">
         <v>46160</v>
       </c>
       <c r="C203" s="3" t="inlineStr">
@@ -6950,7 +6972,7 @@
       <c r="A204" s="3" t="n">
         <v>203</v>
       </c>
-      <c r="B204" s="12" t="n">
+      <c r="B204" s="23" t="n">
         <v>46166</v>
       </c>
       <c r="C204" s="3" t="inlineStr">
@@ -6980,7 +7002,7 @@
       <c r="A205" s="3" t="n">
         <v>204</v>
       </c>
-      <c r="B205" s="12" t="n">
+      <c r="B205" s="23" t="n">
         <v>46167</v>
       </c>
       <c r="C205" s="3" t="inlineStr">
@@ -7010,7 +7032,7 @@
       <c r="A206" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="B206" s="12" t="n">
+      <c r="B206" s="23" t="n">
         <v>46167</v>
       </c>
       <c r="C206" s="3" t="inlineStr">
@@ -7040,7 +7062,7 @@
       <c r="A207" s="3" t="n">
         <v>206</v>
       </c>
-      <c r="B207" s="12" t="n">
+      <c r="B207" s="23" t="n">
         <v>46168</v>
       </c>
       <c r="C207" s="3" t="inlineStr">
@@ -7070,7 +7092,7 @@
       <c r="A208" s="3" t="n">
         <v>207</v>
       </c>
-      <c r="B208" s="12" t="n">
+      <c r="B208" s="23" t="n">
         <v>46172</v>
       </c>
       <c r="C208" s="3" t="inlineStr">
@@ -7100,7 +7122,7 @@
       <c r="A209" s="3" t="n">
         <v>208</v>
       </c>
-      <c r="B209" s="12" t="n">
+      <c r="B209" s="23" t="n">
         <v>46173</v>
       </c>
       <c r="C209" s="3" t="inlineStr">
@@ -7130,7 +7152,7 @@
       <c r="A210" s="3" t="n">
         <v>209</v>
       </c>
-      <c r="B210" s="12" t="n">
+      <c r="B210" s="23" t="n">
         <v>46174</v>
       </c>
       <c r="C210" s="3" t="inlineStr">
@@ -7160,7 +7182,7 @@
       <c r="A211" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="B211" s="12" t="n">
+      <c r="B211" s="23" t="n">
         <v>46175</v>
       </c>
       <c r="C211" s="3" t="inlineStr">
@@ -7190,7 +7212,7 @@
       <c r="A212" s="3" t="n">
         <v>211</v>
       </c>
-      <c r="B212" s="12" t="n">
+      <c r="B212" s="23" t="n">
         <v>46176</v>
       </c>
       <c r="C212" s="3" t="inlineStr">
@@ -7307,7 +7329,7 @@
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="n">
+      <c r="B2" s="23" t="n">
         <v>45983</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -7337,7 +7359,7 @@
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="23" t="n">
         <v>45987</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -7367,7 +7389,7 @@
       <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="23" t="n">
         <v>45989</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -7397,7 +7419,7 @@
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="23" t="n">
         <v>45991</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -7427,7 +7449,7 @@
       <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="23" t="n">
         <v>46002</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -7457,7 +7479,7 @@
       <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="23" t="n">
         <v>46006</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -7487,7 +7509,7 @@
       <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="23" t="n">
         <v>46008</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -7517,7 +7539,7 @@
       <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="23" t="n">
         <v>46021</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -7547,7 +7569,7 @@
       <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="23" t="n">
         <v>46024</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -7577,7 +7599,7 @@
       <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="23" t="n">
         <v>46027</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -7607,7 +7629,7 @@
       <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="23" t="n">
         <v>46037</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -7637,7 +7659,7 @@
       <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="23" t="n">
         <v>46042</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -7667,7 +7689,7 @@
       <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="23" t="n">
         <v>46048</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -7697,7 +7719,7 @@
       <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="23" t="n">
         <v>46053</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -7727,7 +7749,7 @@
       <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="23" t="n">
         <v>46056</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -7757,7 +7779,7 @@
       <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="23" t="n">
         <v>46058</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -7787,7 +7809,7 @@
       <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="23" t="n">
         <v>46062</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -7817,7 +7839,7 @@
       <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="23" t="n">
         <v>46065</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -7847,7 +7869,7 @@
       <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="23" t="n">
         <v>46068</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -7877,7 +7899,7 @@
       <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="23" t="n">
         <v>46071</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -7907,7 +7929,7 @@
       <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="23" t="n">
         <v>46075</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -7937,7 +7959,7 @@
       <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="12" t="n">
+      <c r="B23" s="23" t="n">
         <v>46084</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -7967,7 +7989,7 @@
       <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="23" t="n">
         <v>46085</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -7997,7 +8019,7 @@
       <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="23" t="n">
         <v>46090</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -8027,7 +8049,7 @@
       <c r="A26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="23" t="n">
         <v>46095</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -8057,7 +8079,7 @@
       <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="12" t="n">
+      <c r="B27" s="23" t="n">
         <v>46100</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -8087,7 +8109,7 @@
       <c r="A28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="23" t="n">
         <v>46119</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -8117,7 +8139,7 @@
       <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="23" t="n">
         <v>46125</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -8147,7 +8169,7 @@
       <c r="A30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="23" t="n">
         <v>46128</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -8177,7 +8199,7 @@
       <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="12" t="n">
+      <c r="B31" s="23" t="n">
         <v>46130</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -8207,7 +8229,7 @@
       <c r="A32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="12" t="n">
+      <c r="B32" s="23" t="n">
         <v>46132</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -8237,7 +8259,7 @@
       <c r="A33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="23" t="n">
         <v>46134</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -8267,7 +8289,7 @@
       <c r="A34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="12" t="n">
+      <c r="B34" s="23" t="n">
         <v>46134</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -8297,7 +8319,7 @@
       <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="12" t="n">
+      <c r="B35" s="23" t="n">
         <v>46137</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -8327,7 +8349,7 @@
       <c r="A36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="12" t="n">
+      <c r="B36" s="23" t="n">
         <v>46139</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -8357,7 +8379,7 @@
       <c r="A37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="12" t="n">
+      <c r="B37" s="23" t="n">
         <v>46141</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -8387,7 +8409,7 @@
       <c r="A38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="12" t="n">
+      <c r="B38" s="23" t="n">
         <v>46146</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -8417,7 +8439,7 @@
       <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="23" t="n">
         <v>46148</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -8447,7 +8469,7 @@
       <c r="A40" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="12" t="n">
+      <c r="B40" s="23" t="n">
         <v>46149</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -8477,7 +8499,7 @@
       <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="12" t="n">
+      <c r="B41" s="23" t="n">
         <v>46151</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -8507,7 +8529,7 @@
       <c r="A42" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="12" t="n">
+      <c r="B42" s="23" t="n">
         <v>46154</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -8537,7 +8559,7 @@
       <c r="A43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B43" s="23" t="n">
         <v>46156</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -8567,7 +8589,7 @@
       <c r="A44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="12" t="n">
+      <c r="B44" s="23" t="n">
         <v>46161</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -8597,7 +8619,7 @@
       <c r="A45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="12" t="n">
+      <c r="B45" s="23" t="n">
         <v>46167</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -8627,7 +8649,7 @@
       <c r="A46" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="12" t="n">
+      <c r="B46" s="23" t="n">
         <v>46176</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -8744,7 +8766,7 @@
       <c r="A2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="n">
+      <c r="B2" s="22" t="n">
         <v>45868</v>
       </c>
       <c r="C2" s="9" t="inlineStr">
@@ -8778,7 +8800,7 @@
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="23" t="n">
         <v>45909</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -8808,7 +8830,7 @@
       <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="23" t="n">
         <v>45923</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -8838,7 +8860,7 @@
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="23" t="n">
         <v>45924</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -8868,7 +8890,7 @@
       <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="23" t="n">
         <v>45929</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -8898,7 +8920,7 @@
       <c r="A7" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="22" t="n">
         <v>45935</v>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -8932,7 +8954,7 @@
       <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="23" t="n">
         <v>45938</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -8962,7 +8984,7 @@
       <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="23" t="n">
         <v>45939</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -8992,7 +9014,7 @@
       <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="23" t="n">
         <v>45941</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -9022,7 +9044,7 @@
       <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="23" t="n">
         <v>45943</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -9052,7 +9074,7 @@
       <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="23" t="n">
         <v>45944</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -9082,7 +9104,7 @@
       <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="23" t="n">
         <v>45945</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -9112,7 +9134,7 @@
       <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="12" t="n">
+      <c r="B14" s="23" t="n">
         <v>45946</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -9142,7 +9164,7 @@
       <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="23" t="n">
         <v>45948</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -9172,7 +9194,7 @@
       <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="23" t="n">
         <v>45951</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -9202,7 +9224,7 @@
       <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="23" t="n">
         <v>45952</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -9232,7 +9254,7 @@
       <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="23" t="n">
         <v>45953</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -9262,7 +9284,7 @@
       <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="23" t="n">
         <v>45955</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -9292,7 +9314,7 @@
       <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="23" t="n">
         <v>45956</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -9322,7 +9344,7 @@
       <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="23" t="n">
         <v>45957</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -9352,7 +9374,7 @@
       <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="23" t="n">
         <v>45963</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -9382,7 +9404,7 @@
       <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="12" t="n">
+      <c r="B23" s="23" t="n">
         <v>45966</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -9412,7 +9434,7 @@
       <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="23" t="n">
         <v>45967</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -9442,7 +9464,7 @@
       <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="23" t="n">
         <v>45969</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -9472,7 +9494,7 @@
       <c r="A26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="23" t="n">
         <v>45971</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -9502,7 +9524,7 @@
       <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="12" t="n">
+      <c r="B27" s="23" t="n">
         <v>45972</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -9532,7 +9554,7 @@
       <c r="A28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="23" t="n">
         <v>45973</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -9562,7 +9584,7 @@
       <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="23" t="n">
         <v>45974</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -9592,7 +9614,7 @@
       <c r="A30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="23" t="n">
         <v>45978</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -9622,7 +9644,7 @@
       <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="12" t="n">
+      <c r="B31" s="23" t="n">
         <v>45981</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -9652,7 +9674,7 @@
       <c r="A32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="12" t="n">
+      <c r="B32" s="23" t="n">
         <v>45984</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -9682,7 +9704,7 @@
       <c r="A33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="23" t="n">
         <v>45985</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -9712,7 +9734,7 @@
       <c r="A34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="12" t="n">
+      <c r="B34" s="23" t="n">
         <v>45988</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -9742,7 +9764,7 @@
       <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="12" t="n">
+      <c r="B35" s="23" t="n">
         <v>45996</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -9772,7 +9794,7 @@
       <c r="A36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="12" t="n">
+      <c r="B36" s="23" t="n">
         <v>46006</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -9802,7 +9824,7 @@
       <c r="A37" s="13" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="14" t="n">
+      <c r="B37" s="24" t="n">
         <v>46021</v>
       </c>
       <c r="C37" s="13" t="inlineStr">
@@ -9836,7 +9858,7 @@
       <c r="A38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="12" t="n">
+      <c r="B38" s="23" t="n">
         <v>46058</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -9866,7 +9888,7 @@
       <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="23" t="n">
         <v>46058</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -9896,7 +9918,7 @@
       <c r="A40" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="12" t="n">
+      <c r="B40" s="23" t="n">
         <v>46064</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -9926,7 +9948,7 @@
       <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="12" t="n">
+      <c r="B41" s="23" t="n">
         <v>46072</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -9956,7 +9978,7 @@
       <c r="A42" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="12" t="n">
+      <c r="B42" s="23" t="n">
         <v>46084</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -9986,7 +10008,7 @@
       <c r="A43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B43" s="23" t="n">
         <v>46085</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -10016,7 +10038,7 @@
       <c r="A44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="12" t="n">
+      <c r="B44" s="23" t="n">
         <v>46145</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -10046,7 +10068,7 @@
       <c r="A45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="12" t="n">
+      <c r="B45" s="23" t="n">
         <v>46147</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -10076,7 +10098,7 @@
       <c r="A46" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="12" t="n">
+      <c r="B46" s="23" t="n">
         <v>46152</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -10106,7 +10128,7 @@
       <c r="A47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="12" t="n">
+      <c r="B47" s="23" t="n">
         <v>46154</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -10136,7 +10158,7 @@
       <c r="A48" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="12" t="n">
+      <c r="B48" s="23" t="n">
         <v>46160</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -10189,6 +10211,4438 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J134"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>رقم العقد</t>
+        </is>
+      </c>
+      <c r="B1" s="26" t="inlineStr">
+        <is>
+          <t>تاريخ العقد</t>
+        </is>
+      </c>
+      <c r="C1" s="26" t="inlineStr">
+        <is>
+          <t>رقم الفاتورة المبدئية</t>
+        </is>
+      </c>
+      <c r="D1" s="26" t="inlineStr">
+        <is>
+          <t>كود الصنف</t>
+        </is>
+      </c>
+      <c r="E1" s="26" t="inlineStr">
+        <is>
+          <t>اسم الصنف</t>
+        </is>
+      </c>
+      <c r="F1" s="26" t="inlineStr">
+        <is>
+          <t>الكمية</t>
+        </is>
+      </c>
+      <c r="G1" s="26" t="inlineStr">
+        <is>
+          <t>الوحدة</t>
+        </is>
+      </c>
+      <c r="H1" s="26" t="inlineStr">
+        <is>
+          <t>سعر الوحدة</t>
+        </is>
+      </c>
+      <c r="I1" s="26" t="inlineStr">
+        <is>
+          <t>الإجمالي</t>
+        </is>
+      </c>
+      <c r="J1" s="26" t="inlineStr">
+        <is>
+          <t>ملاحظة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>WHK-1909</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="n">
+        <v>45868</v>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد بنود تفصيلية</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="n"/>
+      <c r="G2" s="9" t="n"/>
+      <c r="H2" s="11" t="n"/>
+      <c r="I2" s="11" t="n">
+        <v>11570</v>
+      </c>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد فاتورة مبدئية لهذا العقد (القيمة من شيت المحاسب WHK2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-1909</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="29" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="6" t="n"/>
+      <c r="I3" s="6">
+        <f>SUM(I2:I2)</f>
+        <v/>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>تاريخه 2025-07-30 قبل بداية الفترة 31-7-2025 بيوم – أُدرج بناءً على طلبك</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2148</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="n">
+        <v>45909</v>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد بنود تفصيلية</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="11" t="n">
+        <v>3320</v>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد فاتورة مبدئية لهذا العقد (القيمة من شيت المحاسب WHK2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2148</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6">
+        <f>SUM(I4:I4)</f>
+        <v/>
+      </c>
+      <c r="J5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2271</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="n">
+        <v>45923</v>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد بنود تفصيلية</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد فاتورة مبدئية لهذا العقد (القيمة من شيت المحاسب WHK2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2271</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="29" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6">
+        <f>SUM(I6:I6)</f>
+        <v/>
+      </c>
+      <c r="J7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2283</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="n">
+        <v>45924</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد بنود تفصيلية</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="11" t="n">
+        <v>2800</v>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد فاتورة مبدئية لهذا العقد (القيمة من شيت المحاسب WHK2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2283</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6">
+        <f>SUM(I8:I8)</f>
+        <v/>
+      </c>
+      <c r="J9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2328</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="n">
+        <v>45929</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد بنود تفصيلية</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="11" t="n"/>
+      <c r="I10" s="11" t="n">
+        <v>4550</v>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد فاتورة مبدئية لهذا العقد (القيمة من شيت المحاسب WHK2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2328</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="29" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6">
+        <f>SUM(I10:I10)</f>
+        <v/>
+      </c>
+      <c r="J11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2364</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>45935</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#40</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F12" s="30" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I12" s="4">
+        <f>F12*H12</f>
+        <v/>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>بالفاتورة رقم العقد WHK-2807 – مسجلة بالكشف على عقد عرعر</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2364</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>45935</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#45</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>41250</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I13" s="4">
+        <f>F13*H13</f>
+        <v/>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>بالفاتورة رقم العقد RNW-2842 – مسجلة بالكشف على عقد عرعر</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2364</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>45935</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#54</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>42000</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I14" s="4">
+        <f>F14*H14</f>
+        <v/>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>بالفاتورة رقم العقد RNW-2945 – مسجلة بالكشف على عقد عرعر</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2364</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="n">
+        <v>45935</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#84</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>42500</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I15" s="4">
+        <f>F15*H15</f>
+        <v/>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>بالفاتورة رقم العقد RNW-3210 – مسجلة بالكشف على عقد عرعر</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2364</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="n">
+        <v>45935</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#100</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F16" s="30" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I16" s="4">
+        <f>F16*H16</f>
+        <v/>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>بالفاتورة رقم العقد RNW-3357 – مسجلة بالكشف على عقد عرعر</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2364</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="n">
+        <v>45935</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#100</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD561</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>زهور مارى جولد</t>
+        </is>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I17" s="4">
+        <f>F17*H17</f>
+        <v/>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>بالفاتورة رقم العقد RNW-3357 – مسجلة بالكشف على عقد عرعر</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2364</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="n">
+        <v>45935</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>كشف الحساب</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>392450</v>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I18" s="11">
+        <f>F18*H18</f>
+        <v/>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>قيد بكشف الحساب بدون فاتورة مبدئية: زهور الجزيرة -392450</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2364</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="n">
+        <v>45935</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>كشف الحساب</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>69625</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I19" s="11">
+        <f>F19*H19</f>
+        <v/>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>قيد بكشف الحساب بدون فاتورة مبدئية: زهور تبوك - 69625*.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2364</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="n">
+        <v>45935</v>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا (رصيد العقد)</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>131265.91</v>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>72196.25</v>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>باقي قيمة العقد 440,000 – لا توجد فاتورة ولا قيد بالكشف (الكمية محسوبة على سعر 0.55)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2364</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="29" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6">
+        <f>SUM(I12:I20)</f>
+        <v/>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>عقد عرعر – أُدرج بالقيمة الكاملة 440,000.00 بناءً على طلبك. المسجل بكشف الحساب (7 قيود) 367,803.75 – الفرق 72,196.25 بدون قيد بالكشف</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2411</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n">
+        <v>45938</v>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد بنود تفصيلية</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="11" t="n"/>
+      <c r="I22" s="11" t="n">
+        <v>4200</v>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد فاتورة مبدئية لهذا العقد (القيمة من شيت المحاسب WHK2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2411</t>
+        </is>
+      </c>
+      <c r="B23" s="28" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="29" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6">
+        <f>SUM(I22:I22)</f>
+        <v/>
+      </c>
+      <c r="J23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2425</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n">
+        <v>45939</v>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد بنود تفصيلية</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="11" t="n"/>
+      <c r="I24" s="11" t="n">
+        <v>11000</v>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد فاتورة مبدئية لهذا العقد (القيمة من شيت المحاسب WHK2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2425</t>
+        </is>
+      </c>
+      <c r="B25" s="28" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="29" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6">
+        <f>SUM(I24:I24)</f>
+        <v/>
+      </c>
+      <c r="J25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2434</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n">
+        <v>45941</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد بنود تفصيلية</t>
+        </is>
+      </c>
+      <c r="F26" s="27" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="11" t="n"/>
+      <c r="I26" s="11" t="n">
+        <v>70250</v>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد فاتورة مبدئية لهذا العقد (القيمة من شيت المحاسب WHK2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2434</t>
+        </is>
+      </c>
+      <c r="B27" s="28" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="29" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6">
+        <f>SUM(I26:I26)</f>
+        <v/>
+      </c>
+      <c r="J27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2465</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n">
+        <v>45943</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد بنود تفصيلية</t>
+        </is>
+      </c>
+      <c r="F28" s="27" t="n"/>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="11" t="n"/>
+      <c r="I28" s="11" t="n">
+        <v>1750</v>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد فاتورة مبدئية لهذا العقد (القيمة من شيت المحاسب WHK2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2465</t>
+        </is>
+      </c>
+      <c r="B29" s="28" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="29" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6">
+        <f>SUM(I28:I28)</f>
+        <v/>
+      </c>
+      <c r="J29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2480</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n">
+        <v>45944</v>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد بنود تفصيلية</t>
+        </is>
+      </c>
+      <c r="F30" s="27" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="11" t="n"/>
+      <c r="I30" s="11" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد فاتورة مبدئية لهذا العقد (القيمة من شيت المحاسب WHK2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2480</t>
+        </is>
+      </c>
+      <c r="B31" s="28" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="29" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6">
+        <f>SUM(I30:I30)</f>
+        <v/>
+      </c>
+      <c r="J31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2498</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n">
+        <v>45945</v>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد بنود تفصيلية</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="11" t="n"/>
+      <c r="I32" s="11" t="n">
+        <v>17055</v>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد فاتورة مبدئية لهذا العقد (القيمة من شيت المحاسب WHK2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2498</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="29" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6">
+        <f>SUM(I32:I32)</f>
+        <v/>
+      </c>
+      <c r="J33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2509</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n">
+        <v>45946</v>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد بنود تفصيلية</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="11" t="n"/>
+      <c r="I34" s="11" t="n">
+        <v>3150</v>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد فاتورة مبدئية لهذا العقد (القيمة من شيت المحاسب WHK2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2509</t>
+        </is>
+      </c>
+      <c r="B35" s="28" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="29" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6">
+        <f>SUM(I34:I34)</f>
+        <v/>
+      </c>
+      <c r="J35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2515</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="n">
+        <v>45948</v>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد بنود تفصيلية</t>
+        </is>
+      </c>
+      <c r="F36" s="27" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="11" t="n"/>
+      <c r="I36" s="11" t="n">
+        <v>6975</v>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد فاتورة مبدئية لهذا العقد (القيمة من شيت المحاسب WHK2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2515</t>
+        </is>
+      </c>
+      <c r="B37" s="28" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="29" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6">
+        <f>SUM(I36:I36)</f>
+        <v/>
+      </c>
+      <c r="J37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2563</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="n">
+        <v>45951</v>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد بنود تفصيلية</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="n"/>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="11" t="n"/>
+      <c r="I38" s="11" t="n">
+        <v>2925</v>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد فاتورة مبدئية لهذا العقد (القيمة من شيت المحاسب WHK2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2563</t>
+        </is>
+      </c>
+      <c r="B39" s="28" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="29" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="6" t="n"/>
+      <c r="I39" s="6">
+        <f>SUM(I38:I38)</f>
+        <v/>
+      </c>
+      <c r="J39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2583</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="n">
+        <v>45952</v>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد بنود تفصيلية</t>
+        </is>
+      </c>
+      <c r="F40" s="27" t="n"/>
+      <c r="G40" s="9" t="n"/>
+      <c r="H40" s="11" t="n"/>
+      <c r="I40" s="11" t="n">
+        <v>4125</v>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد فاتورة مبدئية لهذا العقد (القيمة من شيت المحاسب WHK2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2583</t>
+        </is>
+      </c>
+      <c r="B41" s="28" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="29" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="6" t="n"/>
+      <c r="I41" s="6">
+        <f>SUM(I40:I40)</f>
+        <v/>
+      </c>
+      <c r="J41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2605</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="n">
+        <v>45953</v>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد بنود تفصيلية</t>
+        </is>
+      </c>
+      <c r="F42" s="27" t="n"/>
+      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="11" t="n"/>
+      <c r="I42" s="11" t="n">
+        <v>1331.25</v>
+      </c>
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد فاتورة مبدئية لهذا العقد (القيمة من شيت المحاسب WHK2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2605</t>
+        </is>
+      </c>
+      <c r="B43" s="28" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="29" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="6" t="n"/>
+      <c r="I43" s="6">
+        <f>SUM(I42:I42)</f>
+        <v/>
+      </c>
+      <c r="J43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2626</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="n">
+        <v>45955</v>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد بنود تفصيلية</t>
+        </is>
+      </c>
+      <c r="F44" s="27" t="n"/>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="11" t="n"/>
+      <c r="I44" s="11" t="n">
+        <v>2150</v>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد فاتورة مبدئية لهذا العقد (القيمة من شيت المحاسب WHK2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2626</t>
+        </is>
+      </c>
+      <c r="B45" s="28" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="29" t="n"/>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="6" t="n"/>
+      <c r="I45" s="6">
+        <f>SUM(I44:I44)</f>
+        <v/>
+      </c>
+      <c r="J45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>WHK-2639</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="n">
+        <v>45956</v>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد بنود تفصيلية</t>
+        </is>
+      </c>
+      <c r="F46" s="27" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="11" t="n"/>
+      <c r="I46" s="11" t="n">
+        <v>1125</v>
+      </c>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>لا توجد فاتورة مبدئية لهذا العقد (القيمة من شيت المحاسب WHK2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2639</t>
+        </is>
+      </c>
+      <c r="B47" s="28" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="29" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="6" t="n"/>
+      <c r="I47" s="6">
+        <f>SUM(I46:I46)</f>
+        <v/>
+      </c>
+      <c r="J47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2656</t>
+        </is>
+      </c>
+      <c r="B48" s="23" t="n">
+        <v>45957</v>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#26</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F48" s="30" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I48" s="4">
+        <f>F48*H48</f>
+        <v/>
+      </c>
+      <c r="J48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2656</t>
+        </is>
+      </c>
+      <c r="B49" s="28" t="n"/>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="29" t="n"/>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="6" t="n"/>
+      <c r="I49" s="6">
+        <f>SUM(I48:I48)</f>
+        <v/>
+      </c>
+      <c r="J49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2712</t>
+        </is>
+      </c>
+      <c r="B50" s="23" t="n">
+        <v>45963</v>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#31</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F50" s="30" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I50" s="4">
+        <f>F50*H50</f>
+        <v/>
+      </c>
+      <c r="J50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2712</t>
+        </is>
+      </c>
+      <c r="B51" s="28" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="29" t="n"/>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="6" t="n"/>
+      <c r="I51" s="6">
+        <f>SUM(I50:I50)</f>
+        <v/>
+      </c>
+      <c r="J51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2776</t>
+        </is>
+      </c>
+      <c r="B52" s="23" t="n">
+        <v>45966</v>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#35</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F52" s="30" t="n">
+        <v>1075</v>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I52" s="4">
+        <f>F52*H52</f>
+        <v/>
+      </c>
+      <c r="J52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2776</t>
+        </is>
+      </c>
+      <c r="B53" s="28" t="n"/>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="29" t="n"/>
+      <c r="G53" s="5" t="n"/>
+      <c r="H53" s="6" t="n"/>
+      <c r="I53" s="6">
+        <f>SUM(I52:I52)</f>
+        <v/>
+      </c>
+      <c r="J53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2787</t>
+        </is>
+      </c>
+      <c r="B54" s="23" t="n">
+        <v>45967</v>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#37</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F54" s="30" t="n">
+        <v>450</v>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I54" s="4">
+        <f>F54*H54</f>
+        <v/>
+      </c>
+      <c r="J54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2787</t>
+        </is>
+      </c>
+      <c r="B55" s="28" t="n"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="29" t="n"/>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="6" t="n"/>
+      <c r="I55" s="6">
+        <f>SUM(I54:I54)</f>
+        <v/>
+      </c>
+      <c r="J55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2804</t>
+        </is>
+      </c>
+      <c r="B56" s="23" t="n">
+        <v>45969</v>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#39</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD637</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>زهور سالفيا مركن9 سم</t>
+        </is>
+      </c>
+      <c r="F56" s="30" t="n">
+        <v>2725</v>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I56" s="4">
+        <f>F56*H56</f>
+        <v/>
+      </c>
+      <c r="J56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2804</t>
+        </is>
+      </c>
+      <c r="B57" s="23" t="n">
+        <v>45969</v>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#39</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F57" s="30" t="n">
+        <v>825</v>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I57" s="4">
+        <f>F57*H57</f>
+        <v/>
+      </c>
+      <c r="J57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2804</t>
+        </is>
+      </c>
+      <c r="B58" s="23" t="n">
+        <v>45969</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#39</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD604</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>زهور اقحوان افريقى مركن12 سم</t>
+        </is>
+      </c>
+      <c r="F58" s="30" t="n">
+        <v>3750</v>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I58" s="4">
+        <f>F58*H58</f>
+        <v/>
+      </c>
+      <c r="J58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2804</t>
+        </is>
+      </c>
+      <c r="B59" s="28" t="n"/>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="29" t="n"/>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="6" t="n"/>
+      <c r="I59" s="6">
+        <f>SUM(I56:I58)</f>
+        <v/>
+      </c>
+      <c r="J59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2835</t>
+        </is>
+      </c>
+      <c r="B60" s="23" t="n">
+        <v>45971</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#43</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F60" s="30" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I60" s="4">
+        <f>F60*H60</f>
+        <v/>
+      </c>
+      <c r="J60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2835</t>
+        </is>
+      </c>
+      <c r="B61" s="23" t="n">
+        <v>45971</v>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#43</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD603</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>زهور جرانيوم مركن9 سم</t>
+        </is>
+      </c>
+      <c r="F61" s="30" t="n">
+        <v>900</v>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I61" s="4">
+        <f>F61*H61</f>
+        <v/>
+      </c>
+      <c r="J61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2835</t>
+        </is>
+      </c>
+      <c r="B62" s="23" t="n">
+        <v>45971</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#43</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD620</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>زهور جيرانيوم مركن12 سم</t>
+        </is>
+      </c>
+      <c r="F62" s="30" t="n">
+        <v>500</v>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I62" s="4">
+        <f>F62*H62</f>
+        <v/>
+      </c>
+      <c r="J62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2835</t>
+        </is>
+      </c>
+      <c r="B63" s="23" t="n">
+        <v>45971</v>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#43</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD693</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>زهور جيرانيوم هولندى مركن12 سم</t>
+        </is>
+      </c>
+      <c r="F63" s="30" t="n">
+        <v>500</v>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I63" s="4">
+        <f>F63*H63</f>
+        <v/>
+      </c>
+      <c r="J63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2835</t>
+        </is>
+      </c>
+      <c r="B64" s="23" t="n">
+        <v>45971</v>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#43</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD638</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>زهور هيبوستس مركن9 سم</t>
+        </is>
+      </c>
+      <c r="F64" s="30" t="n">
+        <v>500</v>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I64" s="4">
+        <f>F64*H64</f>
+        <v/>
+      </c>
+      <c r="J64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2835</t>
+        </is>
+      </c>
+      <c r="B65" s="23" t="n">
+        <v>45971</v>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#43</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD604</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>زهور اقحوان افريقى مركن12 سم</t>
+        </is>
+      </c>
+      <c r="F65" s="30" t="n">
+        <v>500</v>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I65" s="4">
+        <f>F65*H65</f>
+        <v/>
+      </c>
+      <c r="J65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2835</t>
+        </is>
+      </c>
+      <c r="B66" s="28" t="n"/>
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="29" t="n"/>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="6" t="n"/>
+      <c r="I66" s="6">
+        <f>SUM(I60:I65)</f>
+        <v/>
+      </c>
+      <c r="J66" s="5" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2853</t>
+        </is>
+      </c>
+      <c r="B67" s="23" t="n">
+        <v>45972</v>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#46</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F67" s="30" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I67" s="4">
+        <f>F67*H67</f>
+        <v/>
+      </c>
+      <c r="J67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2853</t>
+        </is>
+      </c>
+      <c r="B68" s="28" t="n"/>
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="n"/>
+      <c r="F68" s="29" t="n"/>
+      <c r="G68" s="5" t="n"/>
+      <c r="H68" s="6" t="n"/>
+      <c r="I68" s="6">
+        <f>SUM(I67:I67)</f>
+        <v/>
+      </c>
+      <c r="J68" s="5" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2868</t>
+        </is>
+      </c>
+      <c r="B69" s="23" t="n">
+        <v>45973</v>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#47</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F69" s="30" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I69" s="4">
+        <f>F69*H69</f>
+        <v/>
+      </c>
+      <c r="J69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2868</t>
+        </is>
+      </c>
+      <c r="B70" s="28" t="n"/>
+      <c r="C70" s="5" t="n"/>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="5" t="n"/>
+      <c r="F70" s="29" t="n"/>
+      <c r="G70" s="5" t="n"/>
+      <c r="H70" s="6" t="n"/>
+      <c r="I70" s="6">
+        <f>SUM(I69:I69)</f>
+        <v/>
+      </c>
+      <c r="J70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2881</t>
+        </is>
+      </c>
+      <c r="B71" s="23" t="n">
+        <v>45974</v>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#49</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD693</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>زهور جيرانيوم هولندى مركن12 سم</t>
+        </is>
+      </c>
+      <c r="F71" s="30" t="n">
+        <v>510</v>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I71" s="4">
+        <f>F71*H71</f>
+        <v/>
+      </c>
+      <c r="J71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2881</t>
+        </is>
+      </c>
+      <c r="B72" s="28" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="29" t="n"/>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="6" t="n"/>
+      <c r="I72" s="6">
+        <f>SUM(I71:I71)</f>
+        <v/>
+      </c>
+      <c r="J72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2912</t>
+        </is>
+      </c>
+      <c r="B73" s="23" t="n">
+        <v>45978</v>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#52</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F73" s="30" t="n">
+        <v>2600</v>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I73" s="4">
+        <f>F73*H73</f>
+        <v/>
+      </c>
+      <c r="J73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2912</t>
+        </is>
+      </c>
+      <c r="B74" s="23" t="n">
+        <v>45978</v>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#52</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD603</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>زهور جرانيوم مركن9 سم</t>
+        </is>
+      </c>
+      <c r="F74" s="30" t="n">
+        <v>500</v>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I74" s="4">
+        <f>F74*H74</f>
+        <v/>
+      </c>
+      <c r="J74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2912</t>
+        </is>
+      </c>
+      <c r="B75" s="28" t="n"/>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="5" t="n"/>
+      <c r="F75" s="29" t="n"/>
+      <c r="G75" s="5" t="n"/>
+      <c r="H75" s="6" t="n"/>
+      <c r="I75" s="6">
+        <f>SUM(I73:I74)</f>
+        <v/>
+      </c>
+      <c r="J75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2948</t>
+        </is>
+      </c>
+      <c r="B76" s="23" t="n">
+        <v>45981</v>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#55</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I76" s="4">
+        <f>F76*H76</f>
+        <v/>
+      </c>
+      <c r="J76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2948</t>
+        </is>
+      </c>
+      <c r="B77" s="23" t="n">
+        <v>45981</v>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#55</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD603</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>زهور جرانيوم مركن9 سم</t>
+        </is>
+      </c>
+      <c r="F77" s="30" t="n">
+        <v>400</v>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I77" s="4">
+        <f>F77*H77</f>
+        <v/>
+      </c>
+      <c r="J77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2948</t>
+        </is>
+      </c>
+      <c r="B78" s="28" t="n"/>
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="29" t="n"/>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="6" t="n"/>
+      <c r="I78" s="6">
+        <f>SUM(I76:I77)</f>
+        <v/>
+      </c>
+      <c r="J78" s="5" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2971</t>
+        </is>
+      </c>
+      <c r="B79" s="23" t="n">
+        <v>45984</v>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#61</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F79" s="30" t="n">
+        <v>8700</v>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I79" s="4">
+        <f>F79*H79</f>
+        <v/>
+      </c>
+      <c r="J79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2971</t>
+        </is>
+      </c>
+      <c r="B80" s="28" t="n"/>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="29" t="n"/>
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="6" t="n"/>
+      <c r="I80" s="6">
+        <f>SUM(I79:I79)</f>
+        <v/>
+      </c>
+      <c r="J80" s="5" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>WHK-2995</t>
+        </is>
+      </c>
+      <c r="B81" s="23" t="n">
+        <v>45985</v>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#64</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F81" s="30" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I81" s="4">
+        <f>F81*H81</f>
+        <v/>
+      </c>
+      <c r="J81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-2995</t>
+        </is>
+      </c>
+      <c r="B82" s="28" t="n"/>
+      <c r="C82" s="5" t="n"/>
+      <c r="D82" s="5" t="n"/>
+      <c r="E82" s="5" t="n"/>
+      <c r="F82" s="29" t="n"/>
+      <c r="G82" s="5" t="n"/>
+      <c r="H82" s="6" t="n"/>
+      <c r="I82" s="6">
+        <f>SUM(I81:I81)</f>
+        <v/>
+      </c>
+      <c r="J82" s="5" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3029</t>
+        </is>
+      </c>
+      <c r="B83" s="23" t="n">
+        <v>45988</v>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#68</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD561</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>زهور مارى جولد</t>
+        </is>
+      </c>
+      <c r="F83" s="30" t="n">
+        <v>225</v>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I83" s="4">
+        <f>F83*H83</f>
+        <v/>
+      </c>
+      <c r="J83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-3029</t>
+        </is>
+      </c>
+      <c r="B84" s="28" t="n"/>
+      <c r="C84" s="5" t="n"/>
+      <c r="D84" s="5" t="n"/>
+      <c r="E84" s="5" t="n"/>
+      <c r="F84" s="29" t="n"/>
+      <c r="G84" s="5" t="n"/>
+      <c r="H84" s="6" t="n"/>
+      <c r="I84" s="6">
+        <f>SUM(I83:I83)</f>
+        <v/>
+      </c>
+      <c r="J84" s="5" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3135</t>
+        </is>
+      </c>
+      <c r="B85" s="23" t="n">
+        <v>45996</v>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#78</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F85" s="30" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I85" s="4">
+        <f>F85*H85</f>
+        <v/>
+      </c>
+      <c r="J85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-3135</t>
+        </is>
+      </c>
+      <c r="B86" s="28" t="n"/>
+      <c r="C86" s="5" t="n"/>
+      <c r="D86" s="5" t="n"/>
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="29" t="n"/>
+      <c r="G86" s="5" t="n"/>
+      <c r="H86" s="6" t="n"/>
+      <c r="I86" s="6">
+        <f>SUM(I85:I85)</f>
+        <v/>
+      </c>
+      <c r="J86" s="5" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3243</t>
+        </is>
+      </c>
+      <c r="B87" s="23" t="n">
+        <v>46006</v>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#89</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD603</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>زهور جرانيوم مركن9 سم</t>
+        </is>
+      </c>
+      <c r="F87" s="30" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I87" s="4">
+        <f>F87*H87</f>
+        <v/>
+      </c>
+      <c r="J87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-3243</t>
+        </is>
+      </c>
+      <c r="B88" s="28" t="n"/>
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="n"/>
+      <c r="E88" s="5" t="n"/>
+      <c r="F88" s="29" t="n"/>
+      <c r="G88" s="5" t="n"/>
+      <c r="H88" s="6" t="n"/>
+      <c r="I88" s="6">
+        <f>SUM(I87:I87)</f>
+        <v/>
+      </c>
+      <c r="J88" s="5" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3400</t>
+        </is>
+      </c>
+      <c r="B89" s="23" t="n">
+        <v>46021</v>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#103</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>RN-HP-S-WT</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>حجر ديكوري أبيض لامع 1:3 سم (10 كجم)</t>
+        </is>
+      </c>
+      <c r="F89" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I89" s="4">
+        <f>F89*H89</f>
+        <v/>
+      </c>
+      <c r="J89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3400</t>
+        </is>
+      </c>
+      <c r="B90" s="23" t="n">
+        <v>46021</v>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#103</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>RN-HP-S-RD</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>حجر ديكوري أحمر لامع 1:3 سم (10 كجم)</t>
+        </is>
+      </c>
+      <c r="F90" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I90" s="4">
+        <f>F90*H90</f>
+        <v/>
+      </c>
+      <c r="J90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3400</t>
+        </is>
+      </c>
+      <c r="B91" s="23" t="n">
+        <v>46021</v>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#103</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>RN-NP-B-WT</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>حجر ديكوري أبيض مطفي 3:5 سم (10 كجم)</t>
+        </is>
+      </c>
+      <c r="F91" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I91" s="4">
+        <f>F91*H91</f>
+        <v/>
+      </c>
+      <c r="J91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3400</t>
+        </is>
+      </c>
+      <c r="B92" s="23" t="n">
+        <v>46021</v>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#103</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>RN-HP-S-BK</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>حجر ديكوري أسود لامع 1:3 سم (10 كجم)</t>
+        </is>
+      </c>
+      <c r="F92" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I92" s="4">
+        <f>F92*H92</f>
+        <v/>
+      </c>
+      <c r="J92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3400</t>
+        </is>
+      </c>
+      <c r="B93" s="23" t="n">
+        <v>46021</v>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#103</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>RN-NP-S-YW</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>حجر ديكوري أصفر مطفي 1:3 سم (10 كجم)</t>
+        </is>
+      </c>
+      <c r="F93" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I93" s="4">
+        <f>F93*H93</f>
+        <v/>
+      </c>
+      <c r="J93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-3400</t>
+        </is>
+      </c>
+      <c r="B94" s="28" t="n"/>
+      <c r="C94" s="5" t="n"/>
+      <c r="D94" s="5" t="n"/>
+      <c r="E94" s="5" t="n"/>
+      <c r="F94" s="29" t="n"/>
+      <c r="G94" s="5" t="n"/>
+      <c r="H94" s="6" t="n"/>
+      <c r="I94" s="6">
+        <f>SUM(I89:I93)</f>
+        <v/>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>فاتورة مبدئية 103 ومسجلة بكشف الحساب – سقطت من شيت المحاسب</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3758</t>
+        </is>
+      </c>
+      <c r="B95" s="23" t="n">
+        <v>46058</v>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#140</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F95" s="30" t="n">
+        <v>35600</v>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I95" s="4">
+        <f>F95*H95</f>
+        <v/>
+      </c>
+      <c r="J95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3758</t>
+        </is>
+      </c>
+      <c r="B96" s="23" t="n">
+        <v>46058</v>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#140</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD637</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>زهور سالفيا مركن9 سم</t>
+        </is>
+      </c>
+      <c r="F96" s="30" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I96" s="4">
+        <f>F96*H96</f>
+        <v/>
+      </c>
+      <c r="J96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3758</t>
+        </is>
+      </c>
+      <c r="B97" s="23" t="n">
+        <v>46058</v>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#140</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD641</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>زهور قرنفل صيني مركن9 سم</t>
+        </is>
+      </c>
+      <c r="F97" s="30" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I97" s="4">
+        <f>F97*H97</f>
+        <v/>
+      </c>
+      <c r="J97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-3758</t>
+        </is>
+      </c>
+      <c r="B98" s="28" t="n"/>
+      <c r="C98" s="5" t="n"/>
+      <c r="D98" s="5" t="n"/>
+      <c r="E98" s="5" t="n"/>
+      <c r="F98" s="29" t="n"/>
+      <c r="G98" s="5" t="n"/>
+      <c r="H98" s="6" t="n"/>
+      <c r="I98" s="6">
+        <f>SUM(I95:I97)</f>
+        <v/>
+      </c>
+      <c r="J98" s="5" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3760</t>
+        </is>
+      </c>
+      <c r="B99" s="23" t="n">
+        <v>46058</v>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#141</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F99" s="30" t="n">
+        <v>55450</v>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I99" s="4">
+        <f>F99*H99</f>
+        <v/>
+      </c>
+      <c r="J99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3760</t>
+        </is>
+      </c>
+      <c r="B100" s="23" t="n">
+        <v>46058</v>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#141</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD637</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>زهور سالفيا مركن9 سم</t>
+        </is>
+      </c>
+      <c r="F100" s="30" t="n">
+        <v>300</v>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I100" s="4">
+        <f>F100*H100</f>
+        <v/>
+      </c>
+      <c r="J100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3760</t>
+        </is>
+      </c>
+      <c r="B101" s="23" t="n">
+        <v>46058</v>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#141</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD642</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>زهور اليسوم مركن9 سم</t>
+        </is>
+      </c>
+      <c r="F101" s="30" t="n">
+        <v>200</v>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I101" s="4">
+        <f>F101*H101</f>
+        <v/>
+      </c>
+      <c r="J101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3760</t>
+        </is>
+      </c>
+      <c r="B102" s="23" t="n">
+        <v>46058</v>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#141</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD641</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>زهور قرنفل صيني مركن9 سم</t>
+        </is>
+      </c>
+      <c r="F102" s="30" t="n">
+        <v>300</v>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I102" s="4">
+        <f>F102*H102</f>
+        <v/>
+      </c>
+      <c r="J102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3760</t>
+        </is>
+      </c>
+      <c r="B103" s="23" t="n">
+        <v>46058</v>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#141</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD634</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>زهور ملفوف براسيكا مركن9 سم</t>
+        </is>
+      </c>
+      <c r="F103" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I103" s="4">
+        <f>F103*H103</f>
+        <v/>
+      </c>
+      <c r="J103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3760</t>
+        </is>
+      </c>
+      <c r="B104" s="23" t="n">
+        <v>46058</v>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#141</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD643</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>زهور سينيراريا مركن12 سم</t>
+        </is>
+      </c>
+      <c r="F104" s="30" t="n">
+        <v>300</v>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I104" s="4">
+        <f>F104*H104</f>
+        <v/>
+      </c>
+      <c r="J104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3760</t>
+        </is>
+      </c>
+      <c r="B105" s="23" t="n">
+        <v>46058</v>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#141</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD696</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>زهور اقحوان افريقي مركن9 سم</t>
+        </is>
+      </c>
+      <c r="F105" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I105" s="4">
+        <f>F105*H105</f>
+        <v/>
+      </c>
+      <c r="J105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3760</t>
+        </is>
+      </c>
+      <c r="B106" s="23" t="n">
+        <v>46058</v>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#141</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD694</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>كالنشو هولندى مركن12 سم</t>
+        </is>
+      </c>
+      <c r="F106" s="30" t="n">
+        <v>200</v>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I106" s="4">
+        <f>F106*H106</f>
+        <v/>
+      </c>
+      <c r="J106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-3760</t>
+        </is>
+      </c>
+      <c r="B107" s="28" t="n"/>
+      <c r="C107" s="5" t="n"/>
+      <c r="D107" s="5" t="n"/>
+      <c r="E107" s="5" t="n"/>
+      <c r="F107" s="29" t="n"/>
+      <c r="G107" s="5" t="n"/>
+      <c r="H107" s="6" t="n"/>
+      <c r="I107" s="6">
+        <f>SUM(I99:I106)</f>
+        <v/>
+      </c>
+      <c r="J107" s="5" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3809</t>
+        </is>
+      </c>
+      <c r="B108" s="23" t="n">
+        <v>46064</v>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#149</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD603</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>زهور جرانيوم مركن9 سم</t>
+        </is>
+      </c>
+      <c r="F108" s="30" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I108" s="4">
+        <f>F108*H108</f>
+        <v/>
+      </c>
+      <c r="J108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-3809</t>
+        </is>
+      </c>
+      <c r="B109" s="28" t="n"/>
+      <c r="C109" s="5" t="n"/>
+      <c r="D109" s="5" t="n"/>
+      <c r="E109" s="5" t="n"/>
+      <c r="F109" s="29" t="n"/>
+      <c r="G109" s="5" t="n"/>
+      <c r="H109" s="6" t="n"/>
+      <c r="I109" s="6">
+        <f>SUM(I108:I108)</f>
+        <v/>
+      </c>
+      <c r="J109" s="5" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3878</t>
+        </is>
+      </c>
+      <c r="B110" s="23" t="n">
+        <v>46072</v>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#160</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD560</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>زهور بيتونيا</t>
+        </is>
+      </c>
+      <c r="F110" s="30" t="n">
+        <v>4025</v>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I110" s="4">
+        <f>F110*H110</f>
+        <v/>
+      </c>
+      <c r="J110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-3878</t>
+        </is>
+      </c>
+      <c r="B111" s="28" t="n"/>
+      <c r="C111" s="5" t="n"/>
+      <c r="D111" s="5" t="n"/>
+      <c r="E111" s="5" t="n"/>
+      <c r="F111" s="29" t="n"/>
+      <c r="G111" s="5" t="n"/>
+      <c r="H111" s="6" t="n"/>
+      <c r="I111" s="6">
+        <f>SUM(I110:I110)</f>
+        <v/>
+      </c>
+      <c r="J111" s="5" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3923</t>
+        </is>
+      </c>
+      <c r="B112" s="23" t="n">
+        <v>46084</v>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#166</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD696</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>زهور اقحوان افريقي مركن9 سم</t>
+        </is>
+      </c>
+      <c r="F112" s="30" t="n">
+        <v>2075</v>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I112" s="4">
+        <f>F112*H112</f>
+        <v/>
+      </c>
+      <c r="J112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3923</t>
+        </is>
+      </c>
+      <c r="B113" s="23" t="n">
+        <v>46084</v>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#166</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD603</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>زهور جرانيوم مركن9 سم</t>
+        </is>
+      </c>
+      <c r="F113" s="30" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I113" s="4">
+        <f>F113*H113</f>
+        <v/>
+      </c>
+      <c r="J113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-3923</t>
+        </is>
+      </c>
+      <c r="B114" s="28" t="n"/>
+      <c r="C114" s="5" t="n"/>
+      <c r="D114" s="5" t="n"/>
+      <c r="E114" s="5" t="n"/>
+      <c r="F114" s="29" t="n"/>
+      <c r="G114" s="5" t="n"/>
+      <c r="H114" s="6" t="n"/>
+      <c r="I114" s="6">
+        <f>SUM(I112:I113)</f>
+        <v/>
+      </c>
+      <c r="J114" s="5" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3963</t>
+        </is>
+      </c>
+      <c r="B115" s="23" t="n">
+        <v>46085</v>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#174</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD696</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>زهور اقحوان افريقي مركن9 سم</t>
+        </is>
+      </c>
+      <c r="F115" s="30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I115" s="4">
+        <f>F115*H115</f>
+        <v/>
+      </c>
+      <c r="J115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>WHK-3963</t>
+        </is>
+      </c>
+      <c r="B116" s="23" t="n">
+        <v>46085</v>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#174</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD694</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>كالنشو هولندى مركن12 سم</t>
+        </is>
+      </c>
+      <c r="F116" s="30" t="n">
+        <v>300</v>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I116" s="4">
+        <f>F116*H116</f>
+        <v/>
+      </c>
+      <c r="J116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-3963</t>
+        </is>
+      </c>
+      <c r="B117" s="28" t="n"/>
+      <c r="C117" s="5" t="n"/>
+      <c r="D117" s="5" t="n"/>
+      <c r="E117" s="5" t="n"/>
+      <c r="F117" s="29" t="n"/>
+      <c r="G117" s="5" t="n"/>
+      <c r="H117" s="6" t="n"/>
+      <c r="I117" s="6">
+        <f>SUM(I115:I116)</f>
+        <v/>
+      </c>
+      <c r="J117" s="5" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>WHK-4256</t>
+        </is>
+      </c>
+      <c r="B118" s="23" t="n">
+        <v>46145</v>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#227</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD562</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>زهور زينيا</t>
+        </is>
+      </c>
+      <c r="F118" s="30" t="n">
+        <v>25625</v>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I118" s="4">
+        <f>F118*H118</f>
+        <v/>
+      </c>
+      <c r="J118" s="3" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>WHK-4256</t>
+        </is>
+      </c>
+      <c r="B119" s="23" t="n">
+        <v>46145</v>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#227</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD563</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>زهور سيلوزيا</t>
+        </is>
+      </c>
+      <c r="F119" s="30" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I119" s="4">
+        <f>F119*H119</f>
+        <v/>
+      </c>
+      <c r="J119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>WHK-4256</t>
+        </is>
+      </c>
+      <c r="B120" s="23" t="n">
+        <v>46145</v>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#227</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD564</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>زهور امرانتس</t>
+        </is>
+      </c>
+      <c r="F120" s="30" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I120" s="4">
+        <f>F120*H120</f>
+        <v/>
+      </c>
+      <c r="J120" s="3" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>WHK-4256</t>
+        </is>
+      </c>
+      <c r="B121" s="23" t="n">
+        <v>46145</v>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#227</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD565</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>زهور جازانيا</t>
+        </is>
+      </c>
+      <c r="F121" s="30" t="n">
+        <v>4475</v>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I121" s="4">
+        <f>F121*H121</f>
+        <v/>
+      </c>
+      <c r="J121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>WHK-4256</t>
+        </is>
+      </c>
+      <c r="B122" s="23" t="n">
+        <v>46145</v>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#227</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD454</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>تيكوماريا50 سم</t>
+        </is>
+      </c>
+      <c r="F122" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I122" s="4">
+        <f>F122*H122</f>
+        <v/>
+      </c>
+      <c r="J122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>WHK-4256</t>
+        </is>
+      </c>
+      <c r="B123" s="23" t="n">
+        <v>46145</v>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#227</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD623</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>أشجار تيسبيسيا 2-3 متر</t>
+        </is>
+      </c>
+      <c r="F123" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="I123" s="4">
+        <f>F123*H123</f>
+        <v/>
+      </c>
+      <c r="J123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-4256</t>
+        </is>
+      </c>
+      <c r="B124" s="28" t="n"/>
+      <c r="C124" s="5" t="n"/>
+      <c r="D124" s="5" t="n"/>
+      <c r="E124" s="5" t="n"/>
+      <c r="F124" s="29" t="n"/>
+      <c r="G124" s="5" t="n"/>
+      <c r="H124" s="6" t="n"/>
+      <c r="I124" s="6">
+        <f>SUM(I118:I123)</f>
+        <v/>
+      </c>
+      <c r="J124" s="5" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>WHK-4275</t>
+        </is>
+      </c>
+      <c r="B125" s="23" t="n">
+        <v>46147</v>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#231</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD569</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>زهور فينكا روزا</t>
+        </is>
+      </c>
+      <c r="F125" s="30" t="n">
+        <v>37400</v>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I125" s="4">
+        <f>F125*H125</f>
+        <v/>
+      </c>
+      <c r="J125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>WHK-4275</t>
+        </is>
+      </c>
+      <c r="B126" s="23" t="n">
+        <v>46147</v>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#231</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD567</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>زهور كيليوس</t>
+        </is>
+      </c>
+      <c r="F126" s="30" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I126" s="4">
+        <f>F126*H126</f>
+        <v/>
+      </c>
+      <c r="J126" s="3" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-4275</t>
+        </is>
+      </c>
+      <c r="B127" s="28" t="n"/>
+      <c r="C127" s="5" t="n"/>
+      <c r="D127" s="5" t="n"/>
+      <c r="E127" s="5" t="n"/>
+      <c r="F127" s="29" t="n"/>
+      <c r="G127" s="5" t="n"/>
+      <c r="H127" s="6" t="n"/>
+      <c r="I127" s="6">
+        <f>SUM(I125:I126)</f>
+        <v/>
+      </c>
+      <c r="J127" s="5" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>WHK-4291</t>
+        </is>
+      </c>
+      <c r="B128" s="23" t="n">
+        <v>46152</v>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#239</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD569</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>زهور فينكا روزا</t>
+        </is>
+      </c>
+      <c r="F128" s="30" t="n">
+        <v>5700</v>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I128" s="4">
+        <f>F128*H128</f>
+        <v/>
+      </c>
+      <c r="J128" s="3" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-4291</t>
+        </is>
+      </c>
+      <c r="B129" s="28" t="n"/>
+      <c r="C129" s="5" t="n"/>
+      <c r="D129" s="5" t="n"/>
+      <c r="E129" s="5" t="n"/>
+      <c r="F129" s="29" t="n"/>
+      <c r="G129" s="5" t="n"/>
+      <c r="H129" s="6" t="n"/>
+      <c r="I129" s="6">
+        <f>SUM(I128:I128)</f>
+        <v/>
+      </c>
+      <c r="J129" s="5" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>WHK-4305</t>
+        </is>
+      </c>
+      <c r="B130" s="23" t="n">
+        <v>46154</v>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#243</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD569</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>زهور فينكا روزا</t>
+        </is>
+      </c>
+      <c r="F130" s="30" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I130" s="4">
+        <f>F130*H130</f>
+        <v/>
+      </c>
+      <c r="J130" s="3" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-4305</t>
+        </is>
+      </c>
+      <c r="B131" s="28" t="n"/>
+      <c r="C131" s="5" t="n"/>
+      <c r="D131" s="5" t="n"/>
+      <c r="E131" s="5" t="n"/>
+      <c r="F131" s="29" t="n"/>
+      <c r="G131" s="5" t="n"/>
+      <c r="H131" s="6" t="n"/>
+      <c r="I131" s="6">
+        <f>SUM(I130:I130)</f>
+        <v/>
+      </c>
+      <c r="J131" s="5" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>WHK-4323</t>
+        </is>
+      </c>
+      <c r="B132" s="23" t="n">
+        <v>46160</v>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>RN-INV#250</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>RN-OD564</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>زهور امرانتس</t>
+        </is>
+      </c>
+      <c r="F132" s="30" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I132" s="4">
+        <f>F132*H132</f>
+        <v/>
+      </c>
+      <c r="J132" s="3" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>إجمالي العقد WHK-4323</t>
+        </is>
+      </c>
+      <c r="B133" s="28" t="n"/>
+      <c r="C133" s="5" t="n"/>
+      <c r="D133" s="5" t="n"/>
+      <c r="E133" s="5" t="n"/>
+      <c r="F133" s="29" t="n"/>
+      <c r="G133" s="5" t="n"/>
+      <c r="H133" s="6" t="n"/>
+      <c r="I133" s="6">
+        <f>SUM(I132:I132)</f>
+        <v/>
+      </c>
+      <c r="J133" s="5" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="31" t="inlineStr">
+        <is>
+          <t>إجمالي مبيعات أبو خالد</t>
+        </is>
+      </c>
+      <c r="B134" s="32" t="n"/>
+      <c r="C134" s="31" t="n"/>
+      <c r="D134" s="31" t="n"/>
+      <c r="E134" s="31" t="n"/>
+      <c r="F134" s="33" t="n"/>
+      <c r="G134" s="31" t="n"/>
+      <c r="H134" s="34" t="n"/>
+      <c r="I134" s="34">
+        <f>I3+I5+I7+I9+I11+I21+I23+I25+I27+I29+I31+I33+I35+I37+I39+I41+I43+I45+I47+I49+I51+I53+I55+I59+I66+I68+I70+I72+I75+I78+I80+I82+I84+I86+I88+I94+I98+I107+I109+I111+I114+I117+I124+I127+I129+I131+I133</f>
+        <v/>
+      </c>
+      <c r="J134" s="31" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10261,7 +14715,7 @@
           <t>WS-INV-0038</t>
         </is>
       </c>
-      <c r="B2" s="12" t="n">
+      <c r="B2" s="23" t="n">
         <v>46186</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -10302,7 +14756,7 @@
           <t>WS-INV-0035</t>
         </is>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="23" t="n">
         <v>46186</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -10343,7 +14797,7 @@
           <t>WS-INV-0034</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="23" t="n">
         <v>46186</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -10384,7 +14838,7 @@
           <t>WS-INV-0002</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="23" t="n">
         <v>46186</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -10425,7 +14879,7 @@
           <t>WS-INV-0001</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="23" t="n">
         <v>46186</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -10466,7 +14920,7 @@
           <t>WS-INV-0048</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="23" t="n">
         <v>46187</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -10507,7 +14961,7 @@
           <t>WS-INV-0040</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="23" t="n">
         <v>46187</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -10548,7 +15002,7 @@
           <t>WS-INV-0039</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="23" t="n">
         <v>46187</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -10589,7 +15043,7 @@
           <t>WS-INV-0056</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="23" t="n">
         <v>46189</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -10630,7 +15084,7 @@
           <t>WS-INV-0063</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="23" t="n">
         <v>46190</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -10671,7 +15125,7 @@
           <t>WS-INV-0072</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="23" t="n">
         <v>46191</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -10712,7 +15166,7 @@
           <t>WS-INV-0082</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" s="35" t="n">
         <v>46193</v>
       </c>
       <c r="C13" s="19" t="inlineStr">
@@ -10753,7 +15207,7 @@
           <t>WS-INV-0079</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="35" t="n">
         <v>46193</v>
       </c>
       <c r="C14" s="19" t="inlineStr">
@@ -10794,7 +15248,7 @@
           <t>WS-INV-0086</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="23" t="n">
         <v>46194</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -10835,7 +15289,7 @@
           <t>WS-INV-0085</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B16" s="35" t="n">
         <v>46194</v>
       </c>
       <c r="C16" s="19" t="inlineStr">
@@ -10876,7 +15330,7 @@
           <t>WS-INV-0084</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="23" t="n">
         <v>46194</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -10917,7 +15371,7 @@
           <t>WS-INV-0091</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B18" s="23" t="n">
         <v>46195</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -10958,7 +15412,7 @@
           <t>WS-INV-0097</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="23" t="n">
         <v>46196</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -10999,7 +15453,7 @@
           <t>WS-INV-0103</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="23" t="n">
         <v>46197</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11040,7 +15494,7 @@
           <t>WS-INV-0106</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="23" t="n">
         <v>46198</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -11081,7 +15535,7 @@
           <t>WS-INV-0111</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="23" t="n">
         <v>46200</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -11122,7 +15576,7 @@
           <t>WS-INV-0116</t>
         </is>
       </c>
-      <c r="B23" s="12" t="n">
+      <c r="B23" s="23" t="n">
         <v>46201</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -11163,7 +15617,7 @@
           <t>WS-INV-0119</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="23" t="n">
         <v>46202</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11204,7 +15658,7 @@
           <t>WS-INV-0124</t>
         </is>
       </c>
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="23" t="n">
         <v>46203</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11245,7 +15699,7 @@
           <t>WS-INV-0128</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n">
+      <c r="B26" s="23" t="n">
         <v>46204</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -11286,7 +15740,7 @@
           <t>WS-INV-0147</t>
         </is>
       </c>
-      <c r="B27" s="12" t="n">
+      <c r="B27" s="23" t="n">
         <v>46208</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -11327,7 +15781,7 @@
           <t>WS-INV-0143</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n">
+      <c r="B28" s="23" t="n">
         <v>46208</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -11368,7 +15822,7 @@
           <t>WS-INV-0171</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="23" t="n">
         <v>46214</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -11409,7 +15863,7 @@
           <t>WS-INV-0170</t>
         </is>
       </c>
-      <c r="B30" s="12" t="n">
+      <c r="B30" s="23" t="n">
         <v>46214</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -11450,7 +15904,7 @@
           <t>WS-INV-0169</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n">
+      <c r="B31" s="23" t="n">
         <v>46214</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -11491,7 +15945,7 @@
           <t>WS-INV-0178</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n">
+      <c r="B32" s="23" t="n">
         <v>46216</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -11532,7 +15986,7 @@
           <t>WS-INV-0190</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="23" t="n">
         <v>46217</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -11573,7 +16027,7 @@
           <t>WS-INV-0197</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n">
+      <c r="B34" s="23" t="n">
         <v>46219</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -11614,7 +16068,7 @@
           <t>WS-INV-0206</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n">
+      <c r="B35" s="23" t="n">
         <v>46221</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -11655,7 +16109,7 @@
           <t>WS-INV-0215</t>
         </is>
       </c>
-      <c r="B36" s="12" t="n">
+      <c r="B36" s="23" t="n">
         <v>46222</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -11696,7 +16150,7 @@
           <t>WS-INV-0222</t>
         </is>
       </c>
-      <c r="B37" s="12" t="n">
+      <c r="B37" s="23" t="n">
         <v>46224</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -11737,7 +16191,7 @@
           <t>WS-INV-0230</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n">
+      <c r="B38" s="23" t="n">
         <v>46225</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -11778,7 +16232,7 @@
           <t>WS-INV-0233</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="23" t="n">
         <v>46226</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -11819,7 +16273,7 @@
           <t>WS-INV-0237</t>
         </is>
       </c>
-      <c r="B40" s="12" t="n">
+      <c r="B40" s="23" t="n">
         <v>46228</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -11860,7 +16314,7 @@
           <t>WS-INV-0243</t>
         </is>
       </c>
-      <c r="B41" s="12" t="n">
+      <c r="B41" s="23" t="n">
         <v>46229</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -11901,7 +16355,7 @@
           <t>WS-INV-0248</t>
         </is>
       </c>
-      <c r="B42" s="12" t="n">
+      <c r="B42" s="23" t="n">
         <v>46230</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -11942,7 +16396,7 @@
           <t>WS-INV-0250</t>
         </is>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B43" s="23" t="n">
         <v>46231</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -11983,7 +16437,7 @@
           <t>WS-INV-0254</t>
         </is>
       </c>
-      <c r="B44" s="12" t="n">
+      <c r="B44" s="23" t="n">
         <v>46233</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -12024,7 +16478,7 @@
           <t>WS-INV-0074</t>
         </is>
       </c>
-      <c r="B45" s="12" t="n">
+      <c r="B45" s="23" t="n">
         <v>46192</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -12065,7 +16519,7 @@
           <t>WS-INV-0154</t>
         </is>
       </c>
-      <c r="B46" s="12" t="n">
+      <c r="B46" s="23" t="n">
         <v>46210</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -12106,7 +16560,7 @@
           <t>WS-INV-0196</t>
         </is>
       </c>
-      <c r="B47" s="12" t="n">
+      <c r="B47" s="23" t="n">
         <v>46218</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -12147,7 +16601,7 @@
           <t>WS-INV-0198</t>
         </is>
       </c>
-      <c r="B48" s="12" t="n">
+      <c r="B48" s="23" t="n">
         <v>46219</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -12188,7 +16642,7 @@
           <t>WS-INV-0207</t>
         </is>
       </c>
-      <c r="B49" s="12" t="n">
+      <c r="B49" s="23" t="n">
         <v>46221</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12229,7 +16683,7 @@
           <t>WS-INV-0216</t>
         </is>
       </c>
-      <c r="B50" s="12" t="n">
+      <c r="B50" s="23" t="n">
         <v>46222</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12270,7 +16724,7 @@
           <t>WS-INV-0217</t>
         </is>
       </c>
-      <c r="B51" s="12" t="n">
+      <c r="B51" s="23" t="n">
         <v>46223</v>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12311,7 +16765,7 @@
           <t>WS-INV-0223</t>
         </is>
       </c>
-      <c r="B52" s="12" t="n">
+      <c r="B52" s="23" t="n">
         <v>46224</v>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -12352,7 +16806,7 @@
           <t>WS-INV-0231</t>
         </is>
       </c>
-      <c r="B53" s="12" t="n">
+      <c r="B53" s="23" t="n">
         <v>46225</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -12393,7 +16847,7 @@
           <t>WS-INV-0234</t>
         </is>
       </c>
-      <c r="B54" s="12" t="n">
+      <c r="B54" s="23" t="n">
         <v>46226</v>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -12434,7 +16888,7 @@
           <t>WS-INV-0238</t>
         </is>
       </c>
-      <c r="B55" s="12" t="n">
+      <c r="B55" s="23" t="n">
         <v>46228</v>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -12475,7 +16929,7 @@
           <t>WS-INV-0253</t>
         </is>
       </c>
-      <c r="B56" s="12" t="n">
+      <c r="B56" s="23" t="n">
         <v>46232</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -12516,7 +16970,7 @@
           <t>WS-INV-0255</t>
         </is>
       </c>
-      <c r="B57" s="12" t="n">
+      <c r="B57" s="23" t="n">
         <v>46233</v>
       </c>
       <c r="C57" s="3" t="inlineStr">
